--- a/outputs/gestion_requerimientos_scrum_acis_ampliado.xlsx
+++ b/outputs/gestion_requerimientos_scrum_acis_ampliado.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Epicas" sheetId="1" r:id="Rc960033463fd47c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historias de Usuario" sheetId="2" r:id="R075943d25f5c4164"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Epicas" sheetId="1" r:id="Rb886f1c94cfa466a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historias de Usuario" sheetId="2" r:id="R6bdb875c69d647e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flujo OT" sheetId="3" r:id="Rc5232b8e67414671"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,7 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="2">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -25,8 +26,25 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF202020"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF475569"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -36,6 +54,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF5FA"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -51,7 +79,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -67,6 +95,22 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1622,7 +1666,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5d3bf364a0c4ce8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra890be048fd44c2f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1690,22 +1734,22 @@
     </x:row>
     <x:row r="2" ht="76" customHeight="1">
       <x:c r="A2" s="4" t="str">
-        <x:v>HU-01</x:v>
+        <x:v>HU-62</x:v>
       </x:c>
       <x:c r="B2" s="4" t="str">
         <x:v>EP-01</x:v>
       </x:c>
       <x:c r="C2" s="5" t="str">
-        <x:v>Iniciar sesión según perfil</x:v>
+        <x:v>Administrar cuentas del equipo</x:v>
       </x:c>
       <x:c r="D2" s="5" t="str">
-        <x:v>Usuario de ACIS</x:v>
+        <x:v>Jefatura</x:v>
       </x:c>
       <x:c r="E2" s="5" t="str">
-        <x:v>iniciar sesión y ver las funciones de mi perfil</x:v>
+        <x:v>activar o desactivar cuentas de técnicos y planificadores</x:v>
       </x:c>
       <x:c r="F2" s="5" t="str">
-        <x:v>usar solo las OT y acciones autorizadas</x:v>
+        <x:v>controlar quién opera el sistema</x:v>
       </x:c>
       <x:c r="G2" s="4" t="str">
         <x:v>Alta</x:v>
@@ -1714,7 +1758,7 @@
         <x:v>S1 (propuesto)</x:v>
       </x:c>
       <x:c r="I2" s="4" t="str">
-        <x:v>Con credenciales válidas entra al perfil correcto; una cuenta cliente no accede a OT de otros locales; credenciales inválidas no abren sesión.</x:v>
+        <x:v>Se registra perfil y estado de la cuenta; una cuenta inactiva no inicia sesión ni recibe nuevas OT.</x:v>
       </x:c>
       <x:c r="J2" s="4" t="str">
         <x:v>En análisis</x:v>
@@ -1726,7 +1770,7 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M2" s="5" t="str">
-        <x:v>Propuesta a partir de los tres perfiles del caso §3.1. Definir método de autenticación.</x:v>
+        <x:v>Propuesta necesaria para perfiles del caso §3.1; definir autoridad de administración.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="76" customHeight="1">
@@ -1772,22 +1816,22 @@
     </x:row>
     <x:row r="4" ht="76" customHeight="1">
       <x:c r="A4" s="4" t="str">
-        <x:v>HU-03</x:v>
+        <x:v>HU-61</x:v>
       </x:c>
       <x:c r="B4" s="4" t="str">
         <x:v>EP-02</x:v>
       </x:c>
       <x:c r="C4" s="5" t="str">
-        <x:v>Registrar equipo</x:v>
+        <x:v>Registrar local</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
         <x:v>Planificador</x:v>
       </x:c>
       <x:c r="E4" s="5" t="str">
-        <x:v>crear una ficha de equipo vinculada a un local</x:v>
+        <x:v>crear un local para un cliente</x:v>
       </x:c>
       <x:c r="F4" s="5" t="str">
-        <x:v>identificarlo en futuras OT</x:v>
+        <x:v>ubicar correctamente sus equipos y OT</x:v>
       </x:c>
       <x:c r="G4" s="4" t="str">
         <x:v>Alta</x:v>
@@ -1796,7 +1840,7 @@
         <x:v>S2 (propuesto)</x:v>
       </x:c>
       <x:c r="I4" s="4" t="str">
-        <x:v>El equipo pertenece a un local e incluye tipo, identificación, ubicación y fecha de última mantención; no puede asociarse a un local inexistente.</x:v>
+        <x:v>El local exige cliente existente, nombre y dirección; aparece en la ficha del cliente y puede contener equipos.</x:v>
       </x:c>
       <x:c r="J4" s="4" t="str">
         <x:v>Lista</x:v>
@@ -1808,27 +1852,27 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M4" s="5" t="str">
-        <x:v>Caso §3.2. Campo exterior propuesto para clima.</x:v>
+        <x:v>Caso §3.2. Separa cliente y local, antes combinados en HU-02.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="76" customHeight="1">
       <x:c r="A5" s="4" t="str">
-        <x:v>HU-04</x:v>
+        <x:v>HU-03</x:v>
       </x:c>
       <x:c r="B5" s="4" t="str">
-        <x:v>EP-03</x:v>
+        <x:v>EP-02</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>Crear OT</x:v>
+        <x:v>Registrar equipo</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
         <x:v>Planificador</x:v>
       </x:c>
       <x:c r="E5" s="5" t="str">
-        <x:v>crear una orden con equipo, tipo y prioridad</x:v>
+        <x:v>crear una ficha de equipo vinculada a un local</x:v>
       </x:c>
       <x:c r="F5" s="5" t="str">
-        <x:v>formalizar el trabajo solicitado</x:v>
+        <x:v>identificarlo en futuras OT</x:v>
       </x:c>
       <x:c r="G5" s="4" t="str">
         <x:v>Alta</x:v>
@@ -1837,7 +1881,7 @@
         <x:v>S2 (propuesto)</x:v>
       </x:c>
       <x:c r="I5" s="4" t="str">
-        <x:v>La OT exige local y equipo perteneciente a ese local, tipo, prioridad, descripción y fecha prevista; genera ID y estado Creada.</x:v>
+        <x:v>El equipo pertenece a un local e incluye tipo, identificación, ubicación y fecha de última mantención; no puede asociarse a un local inexistente.</x:v>
       </x:c>
       <x:c r="J5" s="4" t="str">
         <x:v>Lista</x:v>
@@ -1849,39 +1893,39 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M5" s="5" t="str">
-        <x:v>Caso §3.1-3.2; campos mínimos propuestos.</x:v>
+        <x:v>Caso §3.2. Campo exterior propuesto para clima.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="76" customHeight="1">
       <x:c r="A6" s="4" t="str">
-        <x:v>HU-05</x:v>
+        <x:v>HU-63</x:v>
       </x:c>
       <x:c r="B6" s="4" t="str">
-        <x:v>EP-03</x:v>
+        <x:v>EP-01</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
-        <x:v>Asignar OT a técnico</x:v>
+        <x:v>Asociar cliente a locales</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
-        <x:v>Planificador</x:v>
+        <x:v>Jefatura</x:v>
       </x:c>
       <x:c r="E6" s="5" t="str">
-        <x:v>asignar una OT a un técnico disponible</x:v>
+        <x:v>asignar a un usuario cliente sus locales autorizados</x:v>
       </x:c>
       <x:c r="F6" s="5" t="str">
-        <x:v>confirmar quién realizará la visita</x:v>
+        <x:v>delimitar qué OT puede consultar</x:v>
       </x:c>
       <x:c r="G6" s="4" t="str">
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="H6" s="4" t="str">
-        <x:v>S2 (propuesto)</x:v>
+        <x:v>S3 (propuesto)</x:v>
       </x:c>
       <x:c r="I6" s="4" t="str">
-        <x:v>Solo técnicos activos pueden recibir la OT; la asignación cambia el estado a Asignada y registra actor y fecha.</x:v>
+        <x:v>Un cliente ve solo OT de locales asociados; al quitar una asociación pierde acceso a esas OT y evidencias.</x:v>
       </x:c>
       <x:c r="J6" s="4" t="str">
-        <x:v>Lista</x:v>
+        <x:v>En análisis</x:v>
       </x:c>
       <x:c r="K6" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -1890,36 +1934,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M6" s="5" t="str">
-        <x:v>Caso §3.1-3.2. Disponibilidad debe definirse.</x:v>
+        <x:v>Propuesta de autorización a partir del caso §3.1.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="76" customHeight="1">
       <x:c r="A7" s="4" t="str">
-        <x:v>HU-06</x:v>
+        <x:v>HU-01</x:v>
       </x:c>
       <x:c r="B7" s="4" t="str">
-        <x:v>EP-03</x:v>
+        <x:v>EP-01</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
-        <x:v>Reprogramar OT</x:v>
+        <x:v>Iniciar sesión según perfil</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
-        <x:v>Planificador</x:v>
+        <x:v>Usuario de ACIS</x:v>
       </x:c>
       <x:c r="E7" s="5" t="str">
-        <x:v>cambiar fecha y hora de una visita</x:v>
+        <x:v>iniciar sesión y ver las funciones de mi perfil</x:v>
       </x:c>
       <x:c r="F7" s="5" t="str">
-        <x:v>mantener la planificación actualizada</x:v>
+        <x:v>usar solo las OT y acciones autorizadas</x:v>
       </x:c>
       <x:c r="G7" s="4" t="str">
-        <x:v>Media</x:v>
+        <x:v>Alta</x:v>
       </x:c>
       <x:c r="H7" s="4" t="str">
-        <x:v>S4 (propuesto)</x:v>
+        <x:v>S1 (propuesto)</x:v>
       </x:c>
       <x:c r="I7" s="4" t="str">
-        <x:v>Reprogramar exige nueva fecha y motivo; conserva la fecha anterior en historial y muestra el cambio al técnico.</x:v>
+        <x:v>La sesión identifica al usuario y su rol; las acciones se muestran según ese rol. La consulta de OT de un cliente requiere además su asociación a locales (HU-63).</x:v>
       </x:c>
       <x:c r="J7" s="4" t="str">
         <x:v>En análisis</x:v>
@@ -1931,39 +1975,39 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M7" s="5" t="str">
-        <x:v>Propuesta. Cancelación separada en HU-65; resolver conflictos offline.</x:v>
+        <x:v>Propuesta a partir de los tres perfiles del caso §3.1. Definir método de autenticación.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="76" customHeight="1">
       <x:c r="A8" s="4" t="str">
-        <x:v>HU-07</x:v>
+        <x:v>HU-64</x:v>
       </x:c>
       <x:c r="B8" s="4" t="str">
-        <x:v>EP-04</x:v>
+        <x:v>EP-01</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
-        <x:v>Consultar mis OT</x:v>
+        <x:v>Cerrar sesión</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
-        <x:v>Técnico</x:v>
+        <x:v>Usuario de ACIS</x:v>
       </x:c>
       <x:c r="E8" s="5" t="str">
-        <x:v>ver mi lista de OT asignadas</x:v>
+        <x:v>cerrar mi sesión en el teléfono</x:v>
       </x:c>
       <x:c r="F8" s="5" t="str">
-        <x:v>organizar mi jornada</x:v>
+        <x:v>impedir uso de mi cuenta por otra persona</x:v>
       </x:c>
       <x:c r="G8" s="4" t="str">
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="H8" s="4" t="str">
-        <x:v>S1 (propuesto)</x:v>
+        <x:v>S2 (propuesto)</x:v>
       </x:c>
       <x:c r="I8" s="4" t="str">
-        <x:v>La lista presenta local, equipo, prioridad, fecha y estado de las OT del técnico autenticado; una OT ajena no aparece.</x:v>
+        <x:v>Al cerrar sesión se vuelve a acceso y no se muestran OT ni fotos locales sin nueva autenticación.</x:v>
       </x:c>
       <x:c r="J8" s="4" t="str">
-        <x:v>En desarrollo</x:v>
+        <x:v>Lista</x:v>
       </x:c>
       <x:c r="K8" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -1972,39 +2016,39 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M8" s="5" t="str">
-        <x:v>La demo Android muestra lista con datos ficticios; falta conexión a usuario y datos reales.</x:v>
+        <x:v>Propuesta complementaria a privacidad del caso §5.1.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="76" customHeight="1">
       <x:c r="A9" s="4" t="str">
-        <x:v>HU-08</x:v>
+        <x:v>HU-59</x:v>
       </x:c>
       <x:c r="B9" s="4" t="str">
-        <x:v>EP-04</x:v>
+        <x:v>EP-09</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
-        <x:v>Consultar detalle de OT</x:v>
+        <x:v>Proteger datos locales</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
         <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E9" s="5" t="str">
-        <x:v>abrir una OT y ver su información</x:v>
+        <x:v>mantener protegidos los registros guardados en el teléfono</x:v>
       </x:c>
       <x:c r="F9" s="5" t="str">
-        <x:v>preparar la visita</x:v>
+        <x:v>evitar acceso indebido si pierdo el dispositivo</x:v>
       </x:c>
       <x:c r="G9" s="4" t="str">
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="H9" s="4" t="str">
-        <x:v>S1 (propuesto)</x:v>
+        <x:v>S2 (propuesto)</x:v>
       </x:c>
       <x:c r="I9" s="4" t="str">
-        <x:v>Al seleccionar una OT se muestran local, equipo, tipo, prioridad, fecha, descripción y estado; se puede volver a la lista.</x:v>
+        <x:v>Los registros y fotos locales quedan asociados al usuario autorizado. Tras cerrar sesión, otra cuenta no puede leerlos; los datos sensibles no se exponen mediante almacenamiento público.</x:v>
       </x:c>
       <x:c r="J9" s="4" t="str">
-        <x:v>En desarrollo</x:v>
+        <x:v>En análisis</x:v>
       </x:c>
       <x:c r="K9" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -2013,36 +2057,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M9" s="5" t="str">
-        <x:v>La navegación lista-detalle existe solo con OT de ejemplo.</x:v>
+        <x:v>Propuesta. Definir cifrado y política de borrado local.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="76" customHeight="1">
       <x:c r="A10" s="4" t="str">
-        <x:v>HU-09</x:v>
+        <x:v>HU-25</x:v>
       </x:c>
       <x:c r="B10" s="4" t="str">
-        <x:v>EP-04</x:v>
+        <x:v>EP-02</x:v>
       </x:c>
       <x:c r="C10" s="5" t="str">
-        <x:v>Aceptar OT</x:v>
+        <x:v>Actualizar datos de local</x:v>
       </x:c>
       <x:c r="D10" s="5" t="str">
-        <x:v>Técnico</x:v>
+        <x:v>Planificador</x:v>
       </x:c>
       <x:c r="E10" s="5" t="str">
-        <x:v>aceptar una OT asignada</x:v>
+        <x:v>corregir dirección y datos del local</x:v>
       </x:c>
       <x:c r="F10" s="5" t="str">
-        <x:v>confirmar que la atenderé</x:v>
+        <x:v>programar visitas con información vigente</x:v>
       </x:c>
       <x:c r="G10" s="4" t="str">
-        <x:v>Alta</x:v>
+        <x:v>Media</x:v>
       </x:c>
       <x:c r="H10" s="4" t="str">
-        <x:v>S1 (propuesto)</x:v>
+        <x:v>S2 (propuesto)</x:v>
       </x:c>
       <x:c r="I10" s="4" t="str">
-        <x:v>Solo el técnico asignado puede aceptar una OT en estado Asignada; se registra aceptación con fecha y hora y cambia a Aceptada.</x:v>
+        <x:v>Al editar un local, el cambio aparece en las OT consultadas después y se conserva su vínculo con cliente.</x:v>
       </x:c>
       <x:c r="J10" s="4" t="str">
         <x:v>Lista</x:v>
@@ -2054,36 +2098,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M10" s="5" t="str">
-        <x:v>Caso §2.4. Transición de estado propuesta.</x:v>
+        <x:v>Propuesta derivada del catastro del caso §3.2.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="76" customHeight="1">
       <x:c r="A11" s="4" t="str">
-        <x:v>HU-10</x:v>
+        <x:v>HU-26</x:v>
       </x:c>
       <x:c r="B11" s="4" t="str">
-        <x:v>EP-04</x:v>
+        <x:v>EP-02</x:v>
       </x:c>
       <x:c r="C11" s="5" t="str">
-        <x:v>Registrar check-in</x:v>
+        <x:v>Actualizar equipo y mantención</x:v>
       </x:c>
       <x:c r="D11" s="5" t="str">
-        <x:v>Técnico</x:v>
+        <x:v>Planificador</x:v>
       </x:c>
       <x:c r="E11" s="5" t="str">
-        <x:v>marcar mi llegada al local</x:v>
+        <x:v>corregir la ficha y última mantención de un equipo</x:v>
       </x:c>
       <x:c r="F11" s="5" t="str">
-        <x:v>dejar constancia del inicio de la visita</x:v>
+        <x:v>planificar con antecedentes vigentes</x:v>
       </x:c>
       <x:c r="G11" s="4" t="str">
-        <x:v>Alta</x:v>
+        <x:v>Media</x:v>
       </x:c>
       <x:c r="H11" s="4" t="str">
         <x:v>S2 (propuesto)</x:v>
       </x:c>
       <x:c r="I11" s="4" t="str">
-        <x:v>En una OT aceptada se registra fecha y hora del check-in incluso sin señal; no se crea un segundo check-in abierto.</x:v>
+        <x:v>La ficha permite actualizar ubicación y fecha de mantención; no se pierde el historial de OT anteriores.</x:v>
       </x:c>
       <x:c r="J11" s="4" t="str">
         <x:v>Lista</x:v>
@@ -2095,36 +2139,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M11" s="5" t="str">
-        <x:v>Caso §3.3. Check-out separado en HU-66.</x:v>
+        <x:v>Propuesta derivada del caso §3.2.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="76" customHeight="1">
       <x:c r="A12" s="4" t="str">
-        <x:v>HU-11</x:v>
+        <x:v>HU-47</x:v>
       </x:c>
       <x:c r="B12" s="4" t="str">
-        <x:v>EP-04</x:v>
+        <x:v>EP-07</x:v>
       </x:c>
       <x:c r="C12" s="5" t="str">
-        <x:v>Registrar diagnóstico</x:v>
+        <x:v>Identificar trabajo exterior</x:v>
       </x:c>
       <x:c r="D12" s="5" t="str">
-        <x:v>Técnico</x:v>
+        <x:v>Planificador</x:v>
       </x:c>
       <x:c r="E12" s="5" t="str">
-        <x:v>anotar diagnóstico de la intervención</x:v>
+        <x:v>marcar si el equipo está expuesto al clima</x:v>
       </x:c>
       <x:c r="F12" s="5" t="str">
-        <x:v>dejar constancia del problema encontrado</x:v>
+        <x:v>aplicar alertas solo donde corresponde</x:v>
       </x:c>
       <x:c r="G12" s="4" t="str">
-        <x:v>Alta</x:v>
+        <x:v>Media</x:v>
       </x:c>
       <x:c r="H12" s="4" t="str">
-        <x:v>S2 (propuesto)</x:v>
+        <x:v>S3 (propuesto)</x:v>
       </x:c>
       <x:c r="I12" s="4" t="str">
-        <x:v>El diagnóstico se guarda como borrador en la OT, incluso en modo avión, y conserva autor y fecha.</x:v>
+        <x:v>La ficha del equipo indica si es exterior; una OT interior no muestra alertas climáticas.</x:v>
       </x:c>
       <x:c r="J12" s="4" t="str">
         <x:v>Lista</x:v>
@@ -2136,27 +2180,27 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M12" s="5" t="str">
-        <x:v>Caso §3.1-3.3.</x:v>
+        <x:v>Propuesta para caso §3.4.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="76" customHeight="1">
       <x:c r="A13" s="4" t="str">
-        <x:v>HU-12</x:v>
+        <x:v>HU-04</x:v>
       </x:c>
       <x:c r="B13" s="4" t="str">
-        <x:v>EP-04</x:v>
+        <x:v>EP-03</x:v>
       </x:c>
       <x:c r="C13" s="5" t="str">
-        <x:v>Registrar actividades</x:v>
+        <x:v>Crear OT</x:v>
       </x:c>
       <x:c r="D13" s="5" t="str">
-        <x:v>Técnico</x:v>
+        <x:v>Planificador</x:v>
       </x:c>
       <x:c r="E13" s="5" t="str">
-        <x:v>anotar las tareas realizadas en una intervención</x:v>
+        <x:v>crear una orden con equipo, tipo y prioridad</x:v>
       </x:c>
       <x:c r="F13" s="5" t="str">
-        <x:v>documentar el trabajo efectuado</x:v>
+        <x:v>formalizar el trabajo solicitado</x:v>
       </x:c>
       <x:c r="G13" s="4" t="str">
         <x:v>Alta</x:v>
@@ -2165,7 +2209,7 @@
         <x:v>S2 (propuesto)</x:v>
       </x:c>
       <x:c r="I13" s="4" t="str">
-        <x:v>Se agregan varias actividades con descripción; pueden guardarse como borrador sin conexión.</x:v>
+        <x:v>La OT exige local y equipo perteneciente a ese local, tipo, prioridad, descripción y fecha prevista; genera ID y estado Creada.</x:v>
       </x:c>
       <x:c r="J13" s="4" t="str">
         <x:v>Lista</x:v>
@@ -2177,27 +2221,27 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M13" s="5" t="str">
-        <x:v>Caso §3.2. Materiales separados en HU-67.</x:v>
+        <x:v>Caso §3.1-3.2; campos mínimos propuestos.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="76" customHeight="1">
       <x:c r="A14" s="4" t="str">
-        <x:v>HU-13</x:v>
+        <x:v>HU-24</x:v>
       </x:c>
       <x:c r="B14" s="4" t="str">
-        <x:v>EP-04</x:v>
+        <x:v>EP-09</x:v>
       </x:c>
       <x:c r="C14" s="5" t="str">
-        <x:v>Adjuntar fotos</x:v>
+        <x:v>Restringir fotos y ubicación por OT</x:v>
       </x:c>
       <x:c r="D14" s="5" t="str">
-        <x:v>Técnico</x:v>
+        <x:v>Usuario autorizado</x:v>
       </x:c>
       <x:c r="E14" s="5" t="str">
-        <x:v>capturar fotos del equipo e intervención</x:v>
+        <x:v>acceder solo a evidencias y ubicación necesarias</x:v>
       </x:c>
       <x:c r="F14" s="5" t="str">
-        <x:v>respaldar el diagnóstico y cierre</x:v>
+        <x:v>proteger datos personales</x:v>
       </x:c>
       <x:c r="G14" s="4" t="str">
         <x:v>Alta</x:v>
@@ -2206,10 +2250,10 @@
         <x:v>S3 (propuesto)</x:v>
       </x:c>
       <x:c r="I14" s="4" t="str">
-        <x:v>Cada foto queda asociada a OT e intervención; se conserva localmente hasta confirmar su envío.</x:v>
+        <x:v>Una persona solo consulta fotos y ubicación de OT autorizadas; una petición a otra OT se rechaza sin entregar el archivo o coordenadas.</x:v>
       </x:c>
       <x:c r="J14" s="4" t="str">
-        <x:v>Lista</x:v>
+        <x:v>En análisis</x:v>
       </x:c>
       <x:c r="K14" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -2218,39 +2262,39 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M14" s="5" t="str">
-        <x:v>Caso §3.1, §3.3. Política de acceso y retención por definir.</x:v>
+        <x:v>Caso §5.1. Definir precisión, conservación y permisos según norma vigente.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="76" customHeight="1">
       <x:c r="A15" s="4" t="str">
-        <x:v>HU-14</x:v>
+        <x:v>HU-20</x:v>
       </x:c>
       <x:c r="B15" s="4" t="str">
-        <x:v>EP-04</x:v>
+        <x:v>EP-07</x:v>
       </x:c>
       <x:c r="C15" s="5" t="str">
-        <x:v>Enviar cierre técnico</x:v>
+        <x:v>Alertar clima al planificar</x:v>
       </x:c>
       <x:c r="D15" s="5" t="str">
-        <x:v>Técnico</x:v>
+        <x:v>Planificador</x:v>
       </x:c>
       <x:c r="E15" s="5" t="str">
-        <x:v>revisar y enviar mi intervención</x:v>
+        <x:v>ver aviso de lluvia o viento al agendar una OT exterior</x:v>
       </x:c>
       <x:c r="F15" s="5" t="str">
-        <x:v>dejar el trabajo listo para conformidad</x:v>
+        <x:v>evaluar otra fecha antes de asignarla</x:v>
       </x:c>
       <x:c r="G15" s="4" t="str">
-        <x:v>Alta</x:v>
+        <x:v>Media</x:v>
       </x:c>
       <x:c r="H15" s="4" t="str">
-        <x:v>S3 (propuesto)</x:v>
+        <x:v>S4 (propuesto)</x:v>
       </x:c>
       <x:c r="I15" s="4" t="str">
-        <x:v>Antes del envío se validan check-in, check-out, diagnóstico y al menos una actividad; se muestran campos faltantes y el estado pasa a Pendiente de conformidad.</x:v>
+        <x:v>Para equipos exteriores y fecha prevista se consulta pronóstico público; se muestran condición, fuente y hora; si falla el servicio se advierte sin bloquear la OT.</x:v>
       </x:c>
       <x:c r="J15" s="4" t="str">
-        <x:v>Lista</x:v>
+        <x:v>En análisis</x:v>
       </x:c>
       <x:c r="K15" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -2259,39 +2303,39 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M15" s="5" t="str">
-        <x:v>Caso §2.4; datos mínimos y flujo de cierre propuestos.</x:v>
+        <x:v>Caso §3.4. Alerta al técnico separada en HU-49; umbrales por definir.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="76" customHeight="1">
       <x:c r="A16" s="4" t="str">
-        <x:v>HU-15</x:v>
+        <x:v>HU-48</x:v>
       </x:c>
       <x:c r="B16" s="4" t="str">
-        <x:v>EP-05</x:v>
+        <x:v>EP-07</x:v>
       </x:c>
       <x:c r="C16" s="5" t="str">
-        <x:v>Guardar visita sin conexión</x:v>
+        <x:v>Ver vigencia del pronóstico</x:v>
       </x:c>
       <x:c r="D16" s="5" t="str">
-        <x:v>Técnico</x:v>
+        <x:v>Planificador</x:v>
       </x:c>
       <x:c r="E16" s="5" t="str">
-        <x:v>usar una OT descargada y guardar la visita en modo avión</x:v>
+        <x:v>conocer fuente y hora de actualización del clima</x:v>
       </x:c>
       <x:c r="F16" s="5" t="str">
-        <x:v>seguir trabajando sin señal</x:v>
+        <x:v>valorar la confianza del aviso</x:v>
       </x:c>
       <x:c r="G16" s="4" t="str">
-        <x:v>Alta</x:v>
+        <x:v>Media</x:v>
       </x:c>
       <x:c r="H16" s="4" t="str">
-        <x:v>S2 (propuesto)</x:v>
+        <x:v>S4 (propuesto)</x:v>
       </x:c>
       <x:c r="I16" s="4" t="str">
-        <x:v>Con OT descargada, el técnico guarda eventos, diagnóstico, actividades, materiales y fotos en modo avión; tras cerrar y abrir la app siguen disponibles.</x:v>
+        <x:v>La alerta muestra proveedor, ubicación, fecha pronosticada y hora de consulta; advierte dato no disponible.</x:v>
       </x:c>
       <x:c r="J16" s="4" t="str">
-        <x:v>Lista</x:v>
+        <x:v>En análisis</x:v>
       </x:c>
       <x:c r="K16" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -2300,39 +2344,39 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M16" s="5" t="str">
-        <x:v>Caso §3.3, §5.1. Descarga previa necesaria.</x:v>
+        <x:v>Caso §3.4. Proveedor por seleccionar.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="76" customHeight="1">
       <x:c r="A17" s="4" t="str">
-        <x:v>HU-16</x:v>
+        <x:v>HU-29</x:v>
       </x:c>
       <x:c r="B17" s="4" t="str">
-        <x:v>EP-05</x:v>
+        <x:v>EP-03</x:v>
       </x:c>
       <x:c r="C17" s="5" t="str">
-        <x:v>Sincronizar automáticamente</x:v>
+        <x:v>Consultar carga por técnico</x:v>
       </x:c>
       <x:c r="D17" s="5" t="str">
-        <x:v>Técnico</x:v>
+        <x:v>Planificador</x:v>
       </x:c>
       <x:c r="E17" s="5" t="str">
-        <x:v>enviar cambios pendientes al recuperar señal</x:v>
+        <x:v>ver visitas asignadas por técnico y día</x:v>
       </x:c>
       <x:c r="F17" s="5" t="str">
-        <x:v>mantener la OT actualizada</x:v>
+        <x:v>distribuir el trabajo</x:v>
       </x:c>
       <x:c r="G17" s="4" t="str">
-        <x:v>Alta</x:v>
+        <x:v>Media</x:v>
       </x:c>
       <x:c r="H17" s="4" t="str">
         <x:v>S3 (propuesto)</x:v>
       </x:c>
       <x:c r="I17" s="4" t="str">
-        <x:v>Al recuperar señal se envían cambios pendientes; cada operación tiene ID único, se confirma una sola vez y no duplica eventos al reintentar.</x:v>
+        <x:v>Se muestran OT por técnico y fecha prevista; las canceladas no cuentan como visitas activas.</x:v>
       </x:c>
       <x:c r="J17" s="4" t="str">
-        <x:v>En análisis</x:v>
+        <x:v>Lista</x:v>
       </x:c>
       <x:c r="K17" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -2341,36 +2385,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M17" s="5" t="str">
-        <x:v>Caso §3.3. Requiere definir backend y política de conflictos.</x:v>
+        <x:v>Propuesta por 4 a 6 locales por jornada, caso §2.1.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="76" customHeight="1">
       <x:c r="A18" s="4" t="str">
-        <x:v>HU-17</x:v>
+        <x:v>HU-30</x:v>
       </x:c>
       <x:c r="B18" s="4" t="str">
-        <x:v>EP-05</x:v>
+        <x:v>EP-03</x:v>
       </x:c>
       <x:c r="C18" s="5" t="str">
-        <x:v>Ver estado de sincronización</x:v>
+        <x:v>Validar asignación</x:v>
       </x:c>
       <x:c r="D18" s="5" t="str">
-        <x:v>Técnico</x:v>
+        <x:v>Planificador</x:v>
       </x:c>
       <x:c r="E18" s="5" t="str">
-        <x:v>distinguir registros pendientes, enviados y con error</x:v>
+        <x:v>detectar una OT sin técnico o equipo válido</x:v>
       </x:c>
       <x:c r="F18" s="5" t="str">
-        <x:v>saber si la información llegó</x:v>
+        <x:v>evitar visitas mal programadas</x:v>
       </x:c>
       <x:c r="G18" s="4" t="str">
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="H18" s="4" t="str">
-        <x:v>S3 (propuesto)</x:v>
+        <x:v>S2 (propuesto)</x:v>
       </x:c>
       <x:c r="I18" s="4" t="str">
-        <x:v>La app indica estado por registro; un error conserva datos locales y ofrece reintento.</x:v>
+        <x:v>Antes de asignar, se comprueba técnico activo, equipo del local y fecha; los errores indican qué corregir.</x:v>
       </x:c>
       <x:c r="J18" s="4" t="str">
         <x:v>Lista</x:v>
@@ -2382,36 +2426,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M18" s="5" t="str">
-        <x:v>Propuesta de usabilidad en docs/planificacion-acis.md.</x:v>
+        <x:v>Regla de calidad propuesta para el caso §3.1-3.2.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="76" customHeight="1">
       <x:c r="A19" s="4" t="str">
-        <x:v>HU-18</x:v>
+        <x:v>HU-05</x:v>
       </x:c>
       <x:c r="B19" s="4" t="str">
-        <x:v>EP-06</x:v>
+        <x:v>EP-03</x:v>
       </x:c>
       <x:c r="C19" s="5" t="str">
-        <x:v>Consultar OT propias</x:v>
+        <x:v>Asignar OT a técnico</x:v>
       </x:c>
       <x:c r="D19" s="5" t="str">
-        <x:v>Cliente</x:v>
+        <x:v>Planificador</x:v>
       </x:c>
       <x:c r="E19" s="5" t="str">
-        <x:v>ver el estado de las OT de mis locales</x:v>
+        <x:v>asignar una OT a un técnico disponible</x:v>
       </x:c>
       <x:c r="F19" s="5" t="str">
-        <x:v>seguir el servicio contratado</x:v>
+        <x:v>confirmar quién realizará la visita</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
-        <x:v>S4 (propuesto)</x:v>
+        <x:v>S2 (propuesto)</x:v>
       </x:c>
       <x:c r="I19" s="4" t="str">
-        <x:v>Solo aparecen OT de locales autorizados; cada una muestra estado, equipo y fecha de actualización.</x:v>
+        <x:v>Solo técnicos activos pueden recibir la OT; la asignación cambia el estado a Asignada y registra actor y fecha.</x:v>
       </x:c>
       <x:c r="J19" s="4" t="str">
         <x:v>Lista</x:v>
@@ -2423,39 +2467,39 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M19" s="5" t="str">
-        <x:v>Caso §3.1. Alcance de permisos por cliente por definir.</x:v>
+        <x:v>Caso §3.1-3.2. Disponibilidad debe definirse.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="76" customHeight="1">
       <x:c r="A20" s="4" t="str">
-        <x:v>HU-19</x:v>
+        <x:v>HU-06</x:v>
       </x:c>
       <x:c r="B20" s="4" t="str">
-        <x:v>EP-06</x:v>
+        <x:v>EP-03</x:v>
       </x:c>
       <x:c r="C20" s="5" t="str">
-        <x:v>Aprobar conformidad</x:v>
+        <x:v>Reprogramar OT</x:v>
       </x:c>
       <x:c r="D20" s="5" t="str">
-        <x:v>Cliente</x:v>
+        <x:v>Planificador</x:v>
       </x:c>
       <x:c r="E20" s="5" t="str">
-        <x:v>aprobar una intervención recibida de mi local</x:v>
+        <x:v>cambiar fecha y hora de una visita</x:v>
       </x:c>
       <x:c r="F20" s="5" t="str">
-        <x:v>validar el servicio realizado</x:v>
+        <x:v>mantener la planificación actualizada</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
-        <x:v>Alta</x:v>
+        <x:v>Media</x:v>
       </x:c>
       <x:c r="H20" s="4" t="str">
         <x:v>S4 (propuesto)</x:v>
       </x:c>
       <x:c r="I20" s="4" t="str">
-        <x:v>Solo el cliente autorizado puede aprobar una intervención enviada; se registran usuario y fecha y la OT queda lista para cierre.</x:v>
+        <x:v>Reprogramar exige nueva fecha y motivo; conserva la fecha anterior en historial y muestra el cambio al técnico.</x:v>
       </x:c>
       <x:c r="J20" s="4" t="str">
-        <x:v>Lista</x:v>
+        <x:v>En análisis</x:v>
       </x:c>
       <x:c r="K20" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -2464,36 +2508,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M20" s="5" t="str">
-        <x:v>Caso §3.1. Observaciones separadas en HU-68.</x:v>
+        <x:v>Propuesta. Cancelación separada en HU-65; resolver conflictos offline.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="76" customHeight="1">
       <x:c r="A21" s="4" t="str">
-        <x:v>HU-20</x:v>
+        <x:v>HU-50</x:v>
       </x:c>
       <x:c r="B21" s="4" t="str">
         <x:v>EP-07</x:v>
       </x:c>
       <x:c r="C21" s="5" t="str">
-        <x:v>Alertar clima al planificar</x:v>
+        <x:v>Revisar alerta al reprogramar</x:v>
       </x:c>
       <x:c r="D21" s="5" t="str">
         <x:v>Planificador</x:v>
       </x:c>
       <x:c r="E21" s="5" t="str">
-        <x:v>ver aviso de lluvia o viento al agendar una OT exterior</x:v>
+        <x:v>actualizar el pronóstico para una nueva fecha</x:v>
       </x:c>
       <x:c r="F21" s="5" t="str">
-        <x:v>evaluar otra fecha antes de asignarla</x:v>
+        <x:v>elegir un momento más seguro</x:v>
       </x:c>
       <x:c r="G21" s="4" t="str">
         <x:v>Media</x:v>
       </x:c>
       <x:c r="H21" s="4" t="str">
-        <x:v>S4 (propuesto)</x:v>
+        <x:v>S5 (propuesto)</x:v>
       </x:c>
       <x:c r="I21" s="4" t="str">
-        <x:v>Para equipos exteriores y fecha prevista se consulta pronóstico público; se muestran condición, fuente y hora; si falla el servicio se advierte sin bloquear la OT.</x:v>
+        <x:v>Al cambiar fecha de una OT exterior se consulta el pronóstico de la nueva fecha y se conserva el motivo del cambio.</x:v>
       </x:c>
       <x:c r="J21" s="4" t="str">
         <x:v>En análisis</x:v>
@@ -2505,27 +2549,27 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M21" s="5" t="str">
-        <x:v>Caso §3.4. Alerta al técnico separada en HU-49; umbrales por definir.</x:v>
+        <x:v>Propuesta. Definir ventana y umbrales.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="76" customHeight="1">
       <x:c r="A22" s="4" t="str">
-        <x:v>HU-21</x:v>
+        <x:v>HU-65</x:v>
       </x:c>
       <x:c r="B22" s="4" t="str">
-        <x:v>EP-08</x:v>
+        <x:v>EP-03</x:v>
       </x:c>
       <x:c r="C22" s="5" t="str">
-        <x:v>Consultar duración de atención</x:v>
+        <x:v>Cancelar OT</x:v>
       </x:c>
       <x:c r="D22" s="5" t="str">
-        <x:v>Jefatura</x:v>
+        <x:v>Planificador</x:v>
       </x:c>
       <x:c r="E22" s="5" t="str">
-        <x:v>ver duración de visitas por OT y cliente</x:v>
+        <x:v>cancelar una visita que ya no se realizará</x:v>
       </x:c>
       <x:c r="F22" s="5" t="str">
-        <x:v>evaluar tiempos reales de ejecución</x:v>
+        <x:v>evitar que el técnico la ejecute</x:v>
       </x:c>
       <x:c r="G22" s="4" t="str">
         <x:v>Media</x:v>
@@ -2534,7 +2578,7 @@
         <x:v>S4 (propuesto)</x:v>
       </x:c>
       <x:c r="I22" s="4" t="str">
-        <x:v>El reporte calcula tiempo entre check-in y check-out de cada visita, muestra período y marca incompleta la visita sin ambos eventos.</x:v>
+        <x:v>Cancelar exige motivo; la OT queda Cancelada, no admite nuevo check-in y el técnico ve el cambio al sincronizar.</x:v>
       </x:c>
       <x:c r="J22" s="4" t="str">
         <x:v>En análisis</x:v>
@@ -2546,39 +2590,39 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M22" s="5" t="str">
-        <x:v>Caso §2.3, §4.1. Diferente de tiempo de respuesta SLA en HU-52.</x:v>
+        <x:v>Propuesta. Definir resolución si el técnico ya inició offline.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="76" customHeight="1">
       <x:c r="A23" s="4" t="str">
-        <x:v>HU-22</x:v>
+        <x:v>HU-07</x:v>
       </x:c>
       <x:c r="B23" s="4" t="str">
-        <x:v>EP-08</x:v>
+        <x:v>EP-04</x:v>
       </x:c>
       <x:c r="C23" s="5" t="str">
-        <x:v>Consultar cumplimiento SLA</x:v>
+        <x:v>Consultar mis OT</x:v>
       </x:c>
       <x:c r="D23" s="5" t="str">
-        <x:v>Jefatura</x:v>
+        <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E23" s="5" t="str">
-        <x:v>ver OT dentro o fuera del plazo contratado</x:v>
+        <x:v>ver mi lista de OT asignadas</x:v>
       </x:c>
       <x:c r="F23" s="5" t="str">
-        <x:v>reportar servicio por cliente</x:v>
+        <x:v>organizar mi jornada</x:v>
       </x:c>
       <x:c r="G23" s="4" t="str">
-        <x:v>Media</x:v>
+        <x:v>Alta</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
-        <x:v>S4 (propuesto)</x:v>
+        <x:v>S2 (propuesto)</x:v>
       </x:c>
       <x:c r="I23" s="4" t="str">
-        <x:v>Para cada OT se muestra la política SLA aplicable, plazo, resultado y causa de exclusión; las OT sin datos suficientes figuran incompletas.</x:v>
+        <x:v>La lista presenta local, equipo, prioridad, fecha y estado de las OT del técnico autenticado; una OT ajena no aparece.</x:v>
       </x:c>
       <x:c r="J23" s="4" t="str">
-        <x:v>En análisis</x:v>
+        <x:v>En desarrollo</x:v>
       </x:c>
       <x:c r="K23" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -2587,39 +2631,39 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M23" s="5" t="str">
-        <x:v>Caso §2.3, §4.1. Regla contractual pendiente; cálculo detallado en HU-52 y HU-53.</x:v>
+        <x:v>La demo Android muestra lista con datos ficticios; falta conexión a usuario y datos reales.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="76" customHeight="1">
       <x:c r="A24" s="4" t="str">
-        <x:v>HU-23</x:v>
+        <x:v>HU-08</x:v>
       </x:c>
       <x:c r="B24" s="4" t="str">
-        <x:v>EP-09</x:v>
+        <x:v>EP-04</x:v>
       </x:c>
       <x:c r="C24" s="5" t="str">
-        <x:v>Ver historial de OT</x:v>
+        <x:v>Consultar detalle de OT</x:v>
       </x:c>
       <x:c r="D24" s="5" t="str">
-        <x:v>Planificador</x:v>
+        <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E24" s="5" t="str">
-        <x:v>consultar eventos y responsables de cada OT</x:v>
+        <x:v>abrir una OT y ver su información</x:v>
       </x:c>
       <x:c r="F24" s="5" t="str">
-        <x:v>reconstruir el ciclo completo</x:v>
+        <x:v>preparar la visita</x:v>
       </x:c>
       <x:c r="G24" s="4" t="str">
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="H24" s="4" t="str">
-        <x:v>S3 (propuesto)</x:v>
+        <x:v>S1 (propuesto)</x:v>
       </x:c>
       <x:c r="I24" s="4" t="str">
-        <x:v>El historial presenta creación, asignación, aceptación, visitas, conformidad y cierre en orden, con actor y fecha de cada evento.</x:v>
+        <x:v>Al seleccionar una OT se muestran local, equipo, tipo, prioridad, fecha, descripción y estado; se puede volver a la lista.</x:v>
       </x:c>
       <x:c r="J24" s="4" t="str">
-        <x:v>Lista</x:v>
+        <x:v>En desarrollo</x:v>
       </x:c>
       <x:c r="K24" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -2628,39 +2672,39 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M24" s="5" t="str">
-        <x:v>Propuesta para trazabilidad exigida por caso §2.3.</x:v>
+        <x:v>La navegación lista-detalle existe solo con OT de ejemplo.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="76" customHeight="1">
       <x:c r="A25" s="4" t="str">
-        <x:v>HU-24</x:v>
+        <x:v>HU-27</x:v>
       </x:c>
       <x:c r="B25" s="4" t="str">
-        <x:v>EP-09</x:v>
+        <x:v>EP-02</x:v>
       </x:c>
       <x:c r="C25" s="5" t="str">
-        <x:v>Restringir fotos y ubicación por OT</x:v>
+        <x:v>Consultar equipos de un local</x:v>
       </x:c>
       <x:c r="D25" s="5" t="str">
-        <x:v>Usuario autorizado</x:v>
+        <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E25" s="5" t="str">
-        <x:v>acceder solo a evidencias y ubicación necesarias</x:v>
+        <x:v>ver los equipos registrados en el local</x:v>
       </x:c>
       <x:c r="F25" s="5" t="str">
-        <x:v>proteger datos personales</x:v>
+        <x:v>identificar el equipo de la OT</x:v>
       </x:c>
       <x:c r="G25" s="4" t="str">
-        <x:v>Alta</x:v>
+        <x:v>Media</x:v>
       </x:c>
       <x:c r="H25" s="4" t="str">
-        <x:v>S3 (propuesto)</x:v>
+        <x:v>S2 (propuesto)</x:v>
       </x:c>
       <x:c r="I25" s="4" t="str">
-        <x:v>Una persona solo consulta fotos y ubicación de OT autorizadas; una petición a otra OT se rechaza sin entregar el archivo o coordenadas.</x:v>
+        <x:v>Desde el detalle de la OT se abre la ficha del equipo correcto con tipo, identificación y ubicación.</x:v>
       </x:c>
       <x:c r="J25" s="4" t="str">
-        <x:v>En análisis</x:v>
+        <x:v>Lista</x:v>
       </x:c>
       <x:c r="K25" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -2669,36 +2713,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M25" s="5" t="str">
-        <x:v>Caso §5.1. Definir precisión, conservación y permisos según norma vigente.</x:v>
+        <x:v>Caso §3.2. Navegación propuesta.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="76" customHeight="1">
       <x:c r="A26" s="4" t="str">
-        <x:v>HU-25</x:v>
+        <x:v>HU-39</x:v>
       </x:c>
       <x:c r="B26" s="4" t="str">
-        <x:v>EP-02</x:v>
+        <x:v>EP-05</x:v>
       </x:c>
       <x:c r="C26" s="5" t="str">
-        <x:v>Actualizar datos de local</x:v>
+        <x:v>Preparar OT sin conexión</x:v>
       </x:c>
       <x:c r="D26" s="5" t="str">
-        <x:v>Planificador</x:v>
+        <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E26" s="5" t="str">
-        <x:v>corregir dirección y datos del local</x:v>
+        <x:v>descargar mis OT antes de salir</x:v>
       </x:c>
       <x:c r="F26" s="5" t="str">
-        <x:v>programar visitas con información vigente</x:v>
+        <x:v>consultarlas al perder señal</x:v>
       </x:c>
       <x:c r="G26" s="4" t="str">
-        <x:v>Media</x:v>
+        <x:v>Alta</x:v>
       </x:c>
       <x:c r="H26" s="4" t="str">
         <x:v>S2 (propuesto)</x:v>
       </x:c>
       <x:c r="I26" s="4" t="str">
-        <x:v>Al editar un local, el cambio aparece en las OT consultadas después y se conserva su vínculo con cliente.</x:v>
+        <x:v>Las OT asignadas, locales y equipos necesarios quedan disponibles en modo avión; se indica la última actualización.</x:v>
       </x:c>
       <x:c r="J26" s="4" t="str">
         <x:v>Lista</x:v>
@@ -2710,39 +2754,39 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M26" s="5" t="str">
-        <x:v>Propuesta derivada del catastro del caso §3.2.</x:v>
+        <x:v>Condición para operación offline del caso §3.3.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="76" customHeight="1">
       <x:c r="A27" s="4" t="str">
-        <x:v>HU-26</x:v>
+        <x:v>HU-31</x:v>
       </x:c>
       <x:c r="B27" s="4" t="str">
-        <x:v>EP-02</x:v>
+        <x:v>EP-03</x:v>
       </x:c>
       <x:c r="C27" s="5" t="str">
-        <x:v>Actualizar equipo y mantención</x:v>
+        <x:v>Avisar cambios de agenda</x:v>
       </x:c>
       <x:c r="D27" s="5" t="str">
-        <x:v>Planificador</x:v>
+        <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E27" s="5" t="str">
-        <x:v>corregir la ficha y última mantención de un equipo</x:v>
+        <x:v>ver cambios de fecha o asignación de mis OT</x:v>
       </x:c>
       <x:c r="F27" s="5" t="str">
-        <x:v>planificar con antecedentes vigentes</x:v>
+        <x:v>ajustar mi jornada</x:v>
       </x:c>
       <x:c r="G27" s="4" t="str">
         <x:v>Media</x:v>
       </x:c>
       <x:c r="H27" s="4" t="str">
-        <x:v>S2 (propuesto)</x:v>
+        <x:v>S4 (propuesto)</x:v>
       </x:c>
       <x:c r="I27" s="4" t="str">
-        <x:v>La ficha permite actualizar ubicación y fecha de mantención; no se pierde el historial de OT anteriores.</x:v>
+        <x:v>La OT muestra la nueva programación y fecha de cambio; si está descargada, se actualiza al sincronizar.</x:v>
       </x:c>
       <x:c r="J27" s="4" t="str">
-        <x:v>Lista</x:v>
+        <x:v>En análisis</x:v>
       </x:c>
       <x:c r="K27" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -2751,36 +2795,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M27" s="5" t="str">
-        <x:v>Propuesta derivada del caso §3.2.</x:v>
+        <x:v>Propuesta. Definir mecanismo de avisos y conflicto offline.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="76" customHeight="1">
       <x:c r="A28" s="4" t="str">
-        <x:v>HU-27</x:v>
+        <x:v>HU-09</x:v>
       </x:c>
       <x:c r="B28" s="4" t="str">
-        <x:v>EP-02</x:v>
+        <x:v>EP-04</x:v>
       </x:c>
       <x:c r="C28" s="5" t="str">
-        <x:v>Consultar equipos de un local</x:v>
+        <x:v>Aceptar OT</x:v>
       </x:c>
       <x:c r="D28" s="5" t="str">
         <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E28" s="5" t="str">
-        <x:v>ver los equipos registrados en el local</x:v>
+        <x:v>aceptar una OT asignada</x:v>
       </x:c>
       <x:c r="F28" s="5" t="str">
-        <x:v>identificar el equipo de la OT</x:v>
+        <x:v>confirmar que la atenderé</x:v>
       </x:c>
       <x:c r="G28" s="4" t="str">
-        <x:v>Media</x:v>
+        <x:v>Alta</x:v>
       </x:c>
       <x:c r="H28" s="4" t="str">
         <x:v>S2 (propuesto)</x:v>
       </x:c>
       <x:c r="I28" s="4" t="str">
-        <x:v>Desde el detalle de la OT se abre la ficha del equipo correcto con tipo, identificación y ubicación.</x:v>
+        <x:v>Solo el técnico asignado puede aceptar una OT en estado Asignada; se registra aceptación con fecha y hora y cambia a Aceptada.</x:v>
       </x:c>
       <x:c r="J28" s="4" t="str">
         <x:v>Lista</x:v>
@@ -2792,39 +2836,39 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M28" s="5" t="str">
-        <x:v>Caso §3.2. Navegación propuesta.</x:v>
+        <x:v>Caso §2.4. Transición de estado propuesta.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="76" customHeight="1">
       <x:c r="A29" s="4" t="str">
-        <x:v>HU-28</x:v>
+        <x:v>HU-49</x:v>
       </x:c>
       <x:c r="B29" s="4" t="str">
-        <x:v>EP-03</x:v>
+        <x:v>EP-07</x:v>
       </x:c>
       <x:c r="C29" s="5" t="str">
-        <x:v>Buscar y filtrar OT</x:v>
+        <x:v>Alertar al técnico</x:v>
       </x:c>
       <x:c r="D29" s="5" t="str">
-        <x:v>Planificador</x:v>
+        <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E29" s="5" t="str">
-        <x:v>filtrar OT por estado, cliente y fecha</x:v>
+        <x:v>ver alerta climática en una OT exterior asignada</x:v>
       </x:c>
       <x:c r="F29" s="5" t="str">
-        <x:v>ubicar trabajos que requieren atención</x:v>
+        <x:v>preparar la visita con seguridad</x:v>
       </x:c>
       <x:c r="G29" s="4" t="str">
         <x:v>Media</x:v>
       </x:c>
       <x:c r="H29" s="4" t="str">
-        <x:v>S3 (propuesto)</x:v>
+        <x:v>S4 (propuesto)</x:v>
       </x:c>
       <x:c r="I29" s="4" t="str">
-        <x:v>Los filtros se combinan; la lista indica filtros activos y permite volver a todas las OT.</x:v>
+        <x:v>Antes de iniciar la visita se muestra aviso vigente de lluvia o viento; no oculta la OT si falla el servicio.</x:v>
       </x:c>
       <x:c r="J29" s="4" t="str">
-        <x:v>Lista</x:v>
+        <x:v>En análisis</x:v>
       </x:c>
       <x:c r="K29" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -2833,36 +2877,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M29" s="5" t="str">
-        <x:v>Propuesta para supervisión del caso §2.4.</x:v>
+        <x:v>Caso §3.4 menciona jefatura y técnico.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="76" customHeight="1">
       <x:c r="A30" s="4" t="str">
-        <x:v>HU-29</x:v>
+        <x:v>HU-33</x:v>
       </x:c>
       <x:c r="B30" s="4" t="str">
-        <x:v>EP-03</x:v>
+        <x:v>EP-04</x:v>
       </x:c>
       <x:c r="C30" s="5" t="str">
-        <x:v>Consultar carga por técnico</x:v>
+        <x:v>Iniciar intervención</x:v>
       </x:c>
       <x:c r="D30" s="5" t="str">
-        <x:v>Planificador</x:v>
+        <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E30" s="5" t="str">
-        <x:v>ver visitas asignadas por técnico y día</x:v>
+        <x:v>abrir una intervención en la OT aceptada</x:v>
       </x:c>
       <x:c r="F30" s="5" t="str">
-        <x:v>distribuir el trabajo</x:v>
+        <x:v>separar cada visita realizada</x:v>
       </x:c>
       <x:c r="G30" s="4" t="str">
-        <x:v>Media</x:v>
+        <x:v>Alta</x:v>
       </x:c>
       <x:c r="H30" s="4" t="str">
-        <x:v>S3 (propuesto)</x:v>
+        <x:v>S2 (propuesto)</x:v>
       </x:c>
       <x:c r="I30" s="4" t="str">
-        <x:v>Se muestran OT por técnico y fecha prevista; las canceladas no cuentan como visitas activas.</x:v>
+        <x:v>En una OT aceptada se abre una intervención con ID, técnico y OT; sus datos no se mezclan con otra visita.</x:v>
       </x:c>
       <x:c r="J30" s="4" t="str">
         <x:v>Lista</x:v>
@@ -2874,27 +2918,27 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M30" s="5" t="str">
-        <x:v>Propuesta por 4 a 6 locales por jornada, caso §2.1.</x:v>
+        <x:v>Propuesta para OT con más de una visita.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="76" customHeight="1">
       <x:c r="A31" s="4" t="str">
-        <x:v>HU-30</x:v>
+        <x:v>HU-57</x:v>
       </x:c>
       <x:c r="B31" s="4" t="str">
-        <x:v>EP-03</x:v>
+        <x:v>EP-09</x:v>
       </x:c>
       <x:c r="C31" s="5" t="str">
-        <x:v>Validar asignación</x:v>
+        <x:v>Solicitar permiso de ubicación</x:v>
       </x:c>
       <x:c r="D31" s="5" t="str">
-        <x:v>Planificador</x:v>
+        <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E31" s="5" t="str">
-        <x:v>detectar una OT sin técnico o equipo válido</x:v>
+        <x:v>autorizar ubicación solo al marcar visita</x:v>
       </x:c>
       <x:c r="F31" s="5" t="str">
-        <x:v>evitar visitas mal programadas</x:v>
+        <x:v>controlar cuándo se registra mi posición</x:v>
       </x:c>
       <x:c r="G31" s="4" t="str">
         <x:v>Alta</x:v>
@@ -2903,10 +2947,10 @@
         <x:v>S2 (propuesto)</x:v>
       </x:c>
       <x:c r="I31" s="4" t="str">
-        <x:v>Antes de asignar, se comprueba técnico activo, equipo del local y fecha; los errores indican qué corregir.</x:v>
+        <x:v>La ubicación se solicita solo al hacer check-in y check-out, con explicación previa. Si el permiso se deniega, se aplica la regla acordada y el resultado queda registrado; no hay seguimiento continuo.</x:v>
       </x:c>
       <x:c r="J31" s="4" t="str">
-        <x:v>Lista</x:v>
+        <x:v>En análisis</x:v>
       </x:c>
       <x:c r="K31" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -2915,39 +2959,39 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M31" s="5" t="str">
-        <x:v>Regla de calidad propuesta para el caso §3.1-3.2.</x:v>
+        <x:v>Caso §5.1. Definir si ubicación es obligatoria.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="76" customHeight="1">
       <x:c r="A32" s="4" t="str">
-        <x:v>HU-31</x:v>
+        <x:v>HU-10</x:v>
       </x:c>
       <x:c r="B32" s="4" t="str">
-        <x:v>EP-03</x:v>
+        <x:v>EP-04</x:v>
       </x:c>
       <x:c r="C32" s="5" t="str">
-        <x:v>Avisar cambios de agenda</x:v>
+        <x:v>Registrar check-in</x:v>
       </x:c>
       <x:c r="D32" s="5" t="str">
         <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E32" s="5" t="str">
-        <x:v>ver cambios de fecha o asignación de mis OT</x:v>
+        <x:v>marcar mi llegada al local</x:v>
       </x:c>
       <x:c r="F32" s="5" t="str">
-        <x:v>ajustar mi jornada</x:v>
+        <x:v>dejar constancia del inicio de la visita</x:v>
       </x:c>
       <x:c r="G32" s="4" t="str">
-        <x:v>Media</x:v>
+        <x:v>Alta</x:v>
       </x:c>
       <x:c r="H32" s="4" t="str">
-        <x:v>S4 (propuesto)</x:v>
+        <x:v>S2 (propuesto)</x:v>
       </x:c>
       <x:c r="I32" s="4" t="str">
-        <x:v>La OT muestra la nueva programación y fecha de cambio; si está descargada, se actualiza al sincronizar.</x:v>
+        <x:v>En una OT aceptada se registra fecha y hora del check-in incluso sin señal; no se crea un segundo check-in abierto.</x:v>
       </x:c>
       <x:c r="J32" s="4" t="str">
-        <x:v>En análisis</x:v>
+        <x:v>Lista</x:v>
       </x:c>
       <x:c r="K32" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -2956,36 +3000,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M32" s="5" t="str">
-        <x:v>Propuesta. Definir mecanismo de avisos y conflicto offline.</x:v>
+        <x:v>Caso §3.3. Check-out separado en HU-66.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="76" customHeight="1">
       <x:c r="A33" s="4" t="str">
-        <x:v>HU-32</x:v>
+        <x:v>HU-34</x:v>
       </x:c>
       <x:c r="B33" s="4" t="str">
-        <x:v>EP-03</x:v>
+        <x:v>EP-04</x:v>
       </x:c>
       <x:c r="C33" s="5" t="str">
-        <x:v>Ver estado operativo de OT</x:v>
+        <x:v>Continuar borrador</x:v>
       </x:c>
       <x:c r="D33" s="5" t="str">
-        <x:v>Planificador</x:v>
+        <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E33" s="5" t="str">
-        <x:v>consultar el estado actual de cada OT</x:v>
+        <x:v>retomar una intervención guardada</x:v>
       </x:c>
       <x:c r="F33" s="5" t="str">
-        <x:v>supervisar avance</x:v>
+        <x:v>completarla entre visitas sin repetir datos</x:v>
       </x:c>
       <x:c r="G33" s="4" t="str">
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="H33" s="4" t="str">
-        <x:v>S3 (propuesto)</x:v>
+        <x:v>S2 (propuesto)</x:v>
       </x:c>
       <x:c r="I33" s="4" t="str">
-        <x:v>La lista muestra estado actual derivado del último evento confirmado; un cambio pendiente de sincronización se identifica como tal.</x:v>
+        <x:v>Al volver a la OT, el borrador conserva los campos ya ingresados y solo el técnico autorizado puede editarlo.</x:v>
       </x:c>
       <x:c r="J33" s="4" t="str">
         <x:v>Lista</x:v>
@@ -2997,27 +3041,27 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M33" s="5" t="str">
-        <x:v>Caso §2.4. Estados detallados propuestos.</x:v>
+        <x:v>Caso §3.3 exige registro rápido; borrador propuesto.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="76" customHeight="1">
       <x:c r="A34" s="4" t="str">
-        <x:v>HU-33</x:v>
+        <x:v>HU-11</x:v>
       </x:c>
       <x:c r="B34" s="4" t="str">
         <x:v>EP-04</x:v>
       </x:c>
       <x:c r="C34" s="5" t="str">
-        <x:v>Iniciar intervención</x:v>
+        <x:v>Registrar diagnóstico</x:v>
       </x:c>
       <x:c r="D34" s="5" t="str">
         <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E34" s="5" t="str">
-        <x:v>abrir una intervención en la OT aceptada</x:v>
+        <x:v>anotar diagnóstico de la intervención</x:v>
       </x:c>
       <x:c r="F34" s="5" t="str">
-        <x:v>separar cada visita realizada</x:v>
+        <x:v>dejar constancia del problema encontrado</x:v>
       </x:c>
       <x:c r="G34" s="4" t="str">
         <x:v>Alta</x:v>
@@ -3026,7 +3070,7 @@
         <x:v>S2 (propuesto)</x:v>
       </x:c>
       <x:c r="I34" s="4" t="str">
-        <x:v>En una OT aceptada se abre una intervención con ID, técnico y OT; sus datos no se mezclan con otra visita.</x:v>
+        <x:v>El diagnóstico se guarda como borrador en la OT, incluso en modo avión, y conserva autor y fecha.</x:v>
       </x:c>
       <x:c r="J34" s="4" t="str">
         <x:v>Lista</x:v>
@@ -3038,27 +3082,27 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M34" s="5" t="str">
-        <x:v>Propuesta para OT con más de una visita.</x:v>
+        <x:v>Caso §3.1-3.3.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="76" customHeight="1">
       <x:c r="A35" s="4" t="str">
-        <x:v>HU-34</x:v>
+        <x:v>HU-12</x:v>
       </x:c>
       <x:c r="B35" s="4" t="str">
         <x:v>EP-04</x:v>
       </x:c>
       <x:c r="C35" s="5" t="str">
-        <x:v>Continuar borrador</x:v>
+        <x:v>Registrar actividades</x:v>
       </x:c>
       <x:c r="D35" s="5" t="str">
         <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E35" s="5" t="str">
-        <x:v>retomar una intervención guardada</x:v>
+        <x:v>anotar las tareas realizadas en una intervención</x:v>
       </x:c>
       <x:c r="F35" s="5" t="str">
-        <x:v>completarla entre visitas sin repetir datos</x:v>
+        <x:v>documentar el trabajo efectuado</x:v>
       </x:c>
       <x:c r="G35" s="4" t="str">
         <x:v>Alta</x:v>
@@ -3067,7 +3111,7 @@
         <x:v>S2 (propuesto)</x:v>
       </x:c>
       <x:c r="I35" s="4" t="str">
-        <x:v>Al volver a la OT, el borrador conserva los campos ya ingresados y solo el técnico autorizado puede editarlo.</x:v>
+        <x:v>Se agregan varias actividades con descripción; pueden guardarse como borrador sin conexión.</x:v>
       </x:c>
       <x:c r="J35" s="4" t="str">
         <x:v>Lista</x:v>
@@ -3079,36 +3123,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M35" s="5" t="str">
-        <x:v>Caso §3.3 exige registro rápido; borrador propuesto.</x:v>
+        <x:v>Caso §3.2. Materiales separados en HU-67.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="76" customHeight="1">
       <x:c r="A36" s="4" t="str">
-        <x:v>HU-35</x:v>
+        <x:v>HU-67</x:v>
       </x:c>
       <x:c r="B36" s="4" t="str">
         <x:v>EP-04</x:v>
       </x:c>
       <x:c r="C36" s="5" t="str">
-        <x:v>Registrar visitas adicionales</x:v>
+        <x:v>Registrar materiales usados</x:v>
       </x:c>
       <x:c r="D36" s="5" t="str">
         <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E36" s="5" t="str">
-        <x:v>agregar otra intervención a una OT abierta</x:v>
+        <x:v>anotar materiales y cantidades de la intervención</x:v>
       </x:c>
       <x:c r="F36" s="5" t="str">
-        <x:v>documentar trabajo en distintas fechas</x:v>
+        <x:v>dejar trazabilidad de lo consumido</x:v>
       </x:c>
       <x:c r="G36" s="4" t="str">
-        <x:v>Media</x:v>
+        <x:v>Alta</x:v>
       </x:c>
       <x:c r="H36" s="4" t="str">
-        <x:v>S4 (propuesto)</x:v>
+        <x:v>S2 (propuesto)</x:v>
       </x:c>
       <x:c r="I36" s="4" t="str">
-        <x:v>Cada visita tiene check-in, check-out, diagnóstico y evidencias propios; la OT muestra ambas en orden.</x:v>
+        <x:v>Cada material incluye nombre o código, cantidad positiva y unidad; puede guardarse sin conexión y editarse en borrador.</x:v>
       </x:c>
       <x:c r="J36" s="4" t="str">
         <x:v>Lista</x:v>
@@ -3120,36 +3164,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M36" s="5" t="str">
-        <x:v>Propuesta del modelo de datos del proyecto.</x:v>
+        <x:v>Caso §3.2. Separada de HU-12.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="76" customHeight="1">
       <x:c r="A37" s="4" t="str">
-        <x:v>HU-36</x:v>
+        <x:v>HU-38</x:v>
       </x:c>
       <x:c r="B37" s="4" t="str">
         <x:v>EP-04</x:v>
       </x:c>
       <x:c r="C37" s="5" t="str">
-        <x:v>Distinguir fotos antes y después</x:v>
+        <x:v>Formulario de registro rápido</x:v>
       </x:c>
       <x:c r="D37" s="5" t="str">
         <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E37" s="5" t="str">
-        <x:v>etiquetar fotos por momento de la intervención</x:v>
+        <x:v>usar un formulario con datos del equipo precargados</x:v>
       </x:c>
       <x:c r="F37" s="5" t="str">
-        <x:v>explicar el resultado del trabajo</x:v>
+        <x:v>registrar la visita entre trabajos</x:v>
       </x:c>
       <x:c r="G37" s="4" t="str">
-        <x:v>Media</x:v>
+        <x:v>Alta</x:v>
       </x:c>
       <x:c r="H37" s="4" t="str">
-        <x:v>S4 (propuesto)</x:v>
+        <x:v>S3 (propuesto)</x:v>
       </x:c>
       <x:c r="I37" s="4" t="str">
-        <x:v>Cada foto puede marcarse antes o después y se muestra con esa etiqueta en el resumen; sigue ligada a la OT.</x:v>
+        <x:v>El formulario precarga local y equipo, muestra primero los datos indispensables y permite guardar sin completar el cierre.</x:v>
       </x:c>
       <x:c r="J37" s="4" t="str">
         <x:v>Lista</x:v>
@@ -3161,27 +3205,27 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M37" s="5" t="str">
-        <x:v>Propuesta para hacer la evidencia más útil.</x:v>
+        <x:v>Caso §3.3 pide registro rápido; estructura del formulario propuesta.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="76" customHeight="1">
       <x:c r="A38" s="4" t="str">
-        <x:v>HU-37</x:v>
+        <x:v>HU-13</x:v>
       </x:c>
       <x:c r="B38" s="4" t="str">
         <x:v>EP-04</x:v>
       </x:c>
       <x:c r="C38" s="5" t="str">
-        <x:v>Revisar resumen antes de enviar</x:v>
+        <x:v>Adjuntar fotos</x:v>
       </x:c>
       <x:c r="D38" s="5" t="str">
         <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E38" s="5" t="str">
-        <x:v>ver diagnóstico, tareas, materiales y fotos reunidos</x:v>
+        <x:v>capturar fotos del equipo e intervención</x:v>
       </x:c>
       <x:c r="F38" s="5" t="str">
-        <x:v>detectar omisiones antes del cierre</x:v>
+        <x:v>respaldar el diagnóstico y cierre</x:v>
       </x:c>
       <x:c r="G38" s="4" t="str">
         <x:v>Alta</x:v>
@@ -3190,7 +3234,7 @@
         <x:v>S3 (propuesto)</x:v>
       </x:c>
       <x:c r="I38" s="4" t="str">
-        <x:v>El resumen muestra todos los registros de la intervención y ofrece volver al apartado incompleto.</x:v>
+        <x:v>Cada foto queda asociada a OT e intervención; se conserva localmente hasta confirmar su envío.</x:v>
       </x:c>
       <x:c r="J38" s="4" t="str">
         <x:v>Lista</x:v>
@@ -3202,36 +3246,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M38" s="5" t="str">
-        <x:v>Propuesta para cierre verificable del caso §2.4.</x:v>
+        <x:v>Caso §3.1, §3.3. Política de acceso y retención por definir.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="76" customHeight="1">
       <x:c r="A39" s="4" t="str">
-        <x:v>HU-38</x:v>
+        <x:v>HU-36</x:v>
       </x:c>
       <x:c r="B39" s="4" t="str">
         <x:v>EP-04</x:v>
       </x:c>
       <x:c r="C39" s="5" t="str">
-        <x:v>Formulario de registro rápido</x:v>
+        <x:v>Distinguir fotos antes y después</x:v>
       </x:c>
       <x:c r="D39" s="5" t="str">
         <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E39" s="5" t="str">
-        <x:v>usar un formulario con datos del equipo precargados</x:v>
+        <x:v>etiquetar fotos por momento de la intervención</x:v>
       </x:c>
       <x:c r="F39" s="5" t="str">
-        <x:v>registrar la visita entre trabajos</x:v>
+        <x:v>explicar el resultado del trabajo</x:v>
       </x:c>
       <x:c r="G39" s="4" t="str">
-        <x:v>Alta</x:v>
+        <x:v>Media</x:v>
       </x:c>
       <x:c r="H39" s="4" t="str">
-        <x:v>S3 (propuesto)</x:v>
+        <x:v>S4 (propuesto)</x:v>
       </x:c>
       <x:c r="I39" s="4" t="str">
-        <x:v>El formulario precarga local y equipo, muestra primero los datos indispensables y permite guardar sin completar el cierre.</x:v>
+        <x:v>Cada foto puede marcarse antes o después y se muestra con esa etiqueta en el resumen; sigue ligada a la OT.</x:v>
       </x:c>
       <x:c r="J39" s="4" t="str">
         <x:v>Lista</x:v>
@@ -3243,27 +3287,27 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M39" s="5" t="str">
-        <x:v>Caso §3.3 pide registro rápido; estructura del formulario propuesta.</x:v>
+        <x:v>Propuesta para hacer la evidencia más útil.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="76" customHeight="1">
       <x:c r="A40" s="4" t="str">
-        <x:v>HU-39</x:v>
+        <x:v>HU-66</x:v>
       </x:c>
       <x:c r="B40" s="4" t="str">
-        <x:v>EP-05</x:v>
+        <x:v>EP-04</x:v>
       </x:c>
       <x:c r="C40" s="5" t="str">
-        <x:v>Preparar OT sin conexión</x:v>
+        <x:v>Registrar check-out</x:v>
       </x:c>
       <x:c r="D40" s="5" t="str">
         <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E40" s="5" t="str">
-        <x:v>descargar mis OT antes de salir</x:v>
+        <x:v>marcar mi salida del local</x:v>
       </x:c>
       <x:c r="F40" s="5" t="str">
-        <x:v>consultarlas al perder señal</x:v>
+        <x:v>cerrar el tiempo de la visita</x:v>
       </x:c>
       <x:c r="G40" s="4" t="str">
         <x:v>Alta</x:v>
@@ -3272,7 +3316,7 @@
         <x:v>S2 (propuesto)</x:v>
       </x:c>
       <x:c r="I40" s="4" t="str">
-        <x:v>Las OT asignadas, locales y equipos necesarios quedan disponibles en modo avión; se indica la última actualización.</x:v>
+        <x:v>Se registra fecha y hora incluso sin señal; requiere check-in previo de la misma visita y no acepta hora anterior.</x:v>
       </x:c>
       <x:c r="J40" s="4" t="str">
         <x:v>Lista</x:v>
@@ -3284,27 +3328,27 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M40" s="5" t="str">
-        <x:v>Condición para operación offline del caso §3.3.</x:v>
+        <x:v>Caso §3.3. Separada de HU-10 para aceptación independiente.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="76" customHeight="1">
       <x:c r="A41" s="4" t="str">
-        <x:v>HU-40</x:v>
+        <x:v>HU-43</x:v>
       </x:c>
       <x:c r="B41" s="4" t="str">
         <x:v>EP-05</x:v>
       </x:c>
       <x:c r="C41" s="5" t="str">
-        <x:v>Reintentar envío fallido</x:v>
+        <x:v>Conservar hora original</x:v>
       </x:c>
       <x:c r="D41" s="5" t="str">
-        <x:v>Técnico</x:v>
+        <x:v>Jefatura</x:v>
       </x:c>
       <x:c r="E41" s="5" t="str">
-        <x:v>reenviar un registro con error</x:v>
+        <x:v>ver cuándo ocurrió un evento offline y cuándo se recibió</x:v>
       </x:c>
       <x:c r="F41" s="5" t="str">
-        <x:v>resolver fallos temporales sin perder trabajo</x:v>
+        <x:v>interpretar correctamente los tiempos</x:v>
       </x:c>
       <x:c r="G41" s="4" t="str">
         <x:v>Alta</x:v>
@@ -3313,7 +3357,7 @@
         <x:v>S3 (propuesto)</x:v>
       </x:c>
       <x:c r="I41" s="4" t="str">
-        <x:v>El reintento conserva el ID de operación; si ya fue confirmado no crea duplicados y muestra resultado.</x:v>
+        <x:v>Todo evento offline conserva fecha y hora registradas en el dispositivo y fecha y hora de recepción del servidor; ambas se distinguen en historial.</x:v>
       </x:c>
       <x:c r="J41" s="4" t="str">
         <x:v>Lista</x:v>
@@ -3325,39 +3369,39 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M41" s="5" t="str">
-        <x:v>Propuesta técnica para sincronización del caso §3.3.</x:v>
+        <x:v>Propuesta para trazabilidad y SLA del caso §2.3.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="76" customHeight="1">
       <x:c r="A42" s="4" t="str">
-        <x:v>HU-41</x:v>
+        <x:v>HU-35</x:v>
       </x:c>
       <x:c r="B42" s="4" t="str">
-        <x:v>EP-05</x:v>
+        <x:v>EP-04</x:v>
       </x:c>
       <x:c r="C42" s="5" t="str">
-        <x:v>Resolver conflicto de OT</x:v>
+        <x:v>Registrar visitas adicionales</x:v>
       </x:c>
       <x:c r="D42" s="5" t="str">
-        <x:v>Planificador</x:v>
+        <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E42" s="5" t="str">
-        <x:v>ver cambios incompatibles hechos sin conexión</x:v>
+        <x:v>agregar otra intervención a una OT abierta</x:v>
       </x:c>
       <x:c r="F42" s="5" t="str">
-        <x:v>decidir el estado correcto de la OT</x:v>
+        <x:v>documentar trabajo en distintas fechas</x:v>
       </x:c>
       <x:c r="G42" s="4" t="str">
-        <x:v>Alta</x:v>
+        <x:v>Media</x:v>
       </x:c>
       <x:c r="H42" s="4" t="str">
-        <x:v>S5 (propuesto)</x:v>
+        <x:v>S4 (propuesto)</x:v>
       </x:c>
       <x:c r="I42" s="4" t="str">
-        <x:v>Al coincidir reasignación o cancelación remota con una visita offline, se muestran ambas versiones; la intervención local no se descarta automáticamente.</x:v>
+        <x:v>Cada visita tiene check-in, check-out, diagnóstico y evidencias propios; la OT muestra ambas en orden.</x:v>
       </x:c>
       <x:c r="J42" s="4" t="str">
-        <x:v>En análisis</x:v>
+        <x:v>Lista</x:v>
       </x:c>
       <x:c r="K42" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -3366,27 +3410,27 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M42" s="5" t="str">
-        <x:v>Propuesta. Falta acordar política de resolución.</x:v>
+        <x:v>Propuesta del modelo de datos del proyecto.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="76" customHeight="1">
       <x:c r="A43" s="4" t="str">
-        <x:v>HU-42</x:v>
+        <x:v>HU-37</x:v>
       </x:c>
       <x:c r="B43" s="4" t="str">
-        <x:v>EP-05</x:v>
+        <x:v>EP-04</x:v>
       </x:c>
       <x:c r="C43" s="5" t="str">
-        <x:v>Sincronizar fotos pendientes</x:v>
+        <x:v>Revisar resumen antes de enviar</x:v>
       </x:c>
       <x:c r="D43" s="5" t="str">
         <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E43" s="5" t="str">
-        <x:v>enviar fotos cuando vuelva la conexión</x:v>
+        <x:v>ver diagnóstico, tareas, materiales y fotos reunidos</x:v>
       </x:c>
       <x:c r="F43" s="5" t="str">
-        <x:v>completar la evidencia de la intervención</x:v>
+        <x:v>detectar omisiones antes del cierre</x:v>
       </x:c>
       <x:c r="G43" s="4" t="str">
         <x:v>Alta</x:v>
@@ -3395,7 +3439,7 @@
         <x:v>S3 (propuesto)</x:v>
       </x:c>
       <x:c r="I43" s="4" t="str">
-        <x:v>Las fotos pendientes se envían por separado; su estado es visible y un fallo no elimina el archivo local.</x:v>
+        <x:v>El resumen muestra todos los registros de la intervención y ofrece volver al apartado incompleto.</x:v>
       </x:c>
       <x:c r="J43" s="4" t="str">
         <x:v>Lista</x:v>
@@ -3407,36 +3451,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M43" s="5" t="str">
-        <x:v>Caso §3.3; estrategia de envío propuesta.</x:v>
+        <x:v>Propuesta para cierre verificable del caso §2.4.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="76" customHeight="1">
       <x:c r="A44" s="4" t="str">
-        <x:v>HU-43</x:v>
+        <x:v>HU-15</x:v>
       </x:c>
       <x:c r="B44" s="4" t="str">
         <x:v>EP-05</x:v>
       </x:c>
       <x:c r="C44" s="5" t="str">
-        <x:v>Conservar hora original</x:v>
+        <x:v>Guardar visita sin conexión</x:v>
       </x:c>
       <x:c r="D44" s="5" t="str">
-        <x:v>Jefatura</x:v>
+        <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E44" s="5" t="str">
-        <x:v>ver cuándo ocurrió un evento offline y cuándo se recibió</x:v>
+        <x:v>usar una OT descargada y guardar la visita en modo avión</x:v>
       </x:c>
       <x:c r="F44" s="5" t="str">
-        <x:v>interpretar correctamente los tiempos</x:v>
+        <x:v>seguir trabajando sin señal</x:v>
       </x:c>
       <x:c r="G44" s="4" t="str">
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="H44" s="4" t="str">
-        <x:v>S5 (propuesto)</x:v>
+        <x:v>S3 (propuesto)</x:v>
       </x:c>
       <x:c r="I44" s="4" t="str">
-        <x:v>Todo evento offline conserva fecha y hora registradas en el dispositivo y fecha y hora de recepción del servidor; ambas se distinguen en historial.</x:v>
+        <x:v>Sin conexión se guardan en el dispositivo eventos, diagnóstico, actividades, materiales y fotos con identificador único. La información sobrevive al cierre de la app y distingue pendiente de confirmada.</x:v>
       </x:c>
       <x:c r="J44" s="4" t="str">
         <x:v>Lista</x:v>
@@ -3448,36 +3492,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M44" s="5" t="str">
-        <x:v>Propuesta para trazabilidad y SLA del caso §2.3.</x:v>
+        <x:v>Caso §3.3, §5.1. Descarga previa necesaria.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="76" customHeight="1">
       <x:c r="A45" s="4" t="str">
-        <x:v>HU-44</x:v>
+        <x:v>HU-14</x:v>
       </x:c>
       <x:c r="B45" s="4" t="str">
-        <x:v>EP-06</x:v>
+        <x:v>EP-04</x:v>
       </x:c>
       <x:c r="C45" s="5" t="str">
-        <x:v>Revisar intervención recibida</x:v>
+        <x:v>Enviar cierre técnico</x:v>
       </x:c>
       <x:c r="D45" s="5" t="str">
-        <x:v>Cliente</x:v>
+        <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E45" s="5" t="str">
-        <x:v>ver resumen y evidencias de una OT de mi local</x:v>
+        <x:v>revisar y enviar mi intervención</x:v>
       </x:c>
       <x:c r="F45" s="5" t="str">
-        <x:v>evaluar la conformidad</x:v>
+        <x:v>dejar el trabajo listo para conformidad</x:v>
       </x:c>
       <x:c r="G45" s="4" t="str">
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="H45" s="4" t="str">
-        <x:v>S4 (propuesto)</x:v>
+        <x:v>S3 (propuesto)</x:v>
       </x:c>
       <x:c r="I45" s="4" t="str">
-        <x:v>El cliente autorizado abre solo intervenciones enviadas de sus locales y revisa diagnóstico, actividades, materiales y fotos confirmadas.</x:v>
+        <x:v>Antes de enviar se exige check-in, check-out, diagnóstico y al menos una actividad. El envío local queda pendiente hasta confirmación remota; solo entonces la OT pasa a pendiente de conformidad. Una visita no ejecutada sigue HU-70.</x:v>
       </x:c>
       <x:c r="J45" s="4" t="str">
         <x:v>Lista</x:v>
@@ -3489,36 +3533,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M45" s="5" t="str">
-        <x:v>Caso §3.1; detalle de revisión propuesto.</x:v>
+        <x:v>Caso §2.4; datos mínimos y flujo de cierre propuestos.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="76" customHeight="1">
       <x:c r="A46" s="4" t="str">
-        <x:v>HU-45</x:v>
+        <x:v>HU-16</x:v>
       </x:c>
       <x:c r="B46" s="4" t="str">
-        <x:v>EP-06</x:v>
+        <x:v>EP-05</x:v>
       </x:c>
       <x:c r="C46" s="5" t="str">
-        <x:v>Responder observaciones</x:v>
+        <x:v>Sincronizar automáticamente</x:v>
       </x:c>
       <x:c r="D46" s="5" t="str">
         <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E46" s="5" t="str">
-        <x:v>ver observaciones del cliente y registrar respuesta</x:v>
+        <x:v>enviar cambios pendientes al recuperar señal</x:v>
       </x:c>
       <x:c r="F46" s="5" t="str">
-        <x:v>resolver lo pendiente antes del cierre</x:v>
+        <x:v>mantener la OT actualizada</x:v>
       </x:c>
       <x:c r="G46" s="4" t="str">
-        <x:v>Media</x:v>
+        <x:v>Alta</x:v>
       </x:c>
       <x:c r="H46" s="4" t="str">
-        <x:v>S5 (propuesto)</x:v>
+        <x:v>S3 (propuesto)</x:v>
       </x:c>
       <x:c r="I46" s="4" t="str">
-        <x:v>Una OT observada muestra comentario, autor y fecha; el técnico responde y la nueva revisión vuelve a Pendiente de conformidad.</x:v>
+        <x:v>Las operaciones pendientes se envían al recuperar conexión con identificadores únicos; los reintentos no duplican visitas, eventos ni fotos. El estado pasa a confirmado solo tras respuesta remota.</x:v>
       </x:c>
       <x:c r="J46" s="4" t="str">
         <x:v>En análisis</x:v>
@@ -3530,36 +3574,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M46" s="5" t="str">
-        <x:v>Propuesta. Definir si exige nueva visita.</x:v>
+        <x:v>Caso §3.3. Requiere definir backend y política de conflictos.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="76" customHeight="1">
       <x:c r="A47" s="4" t="str">
-        <x:v>HU-46</x:v>
+        <x:v>HU-40</x:v>
       </x:c>
       <x:c r="B47" s="4" t="str">
-        <x:v>EP-06</x:v>
+        <x:v>EP-05</x:v>
       </x:c>
       <x:c r="C47" s="5" t="str">
-        <x:v>Cerrar OT conforme</x:v>
+        <x:v>Reintentar envío fallido</x:v>
       </x:c>
       <x:c r="D47" s="5" t="str">
-        <x:v>Planificador</x:v>
+        <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E47" s="5" t="str">
-        <x:v>cerrar una OT tras la conformidad del cliente</x:v>
+        <x:v>reenviar un registro con error</x:v>
       </x:c>
       <x:c r="F47" s="5" t="str">
-        <x:v>completar el ciclo verificablemente</x:v>
+        <x:v>resolver fallos temporales sin perder trabajo</x:v>
       </x:c>
       <x:c r="G47" s="4" t="str">
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="H47" s="4" t="str">
-        <x:v>S5 (propuesto)</x:v>
+        <x:v>S3 (propuesto)</x:v>
       </x:c>
       <x:c r="I47" s="4" t="str">
-        <x:v>Solo una OT con conformidad aprobada puede cerrarse; una OT con observaciones abiertas no se cierra y cada transición queda en historial.</x:v>
+        <x:v>El reintento conserva el ID de operación; si ya fue confirmado no crea duplicados y muestra resultado.</x:v>
       </x:c>
       <x:c r="J47" s="4" t="str">
         <x:v>Lista</x:v>
@@ -3571,36 +3615,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M47" s="5" t="str">
-        <x:v>Regla de flujo propuesta desde caso §3.1.</x:v>
+        <x:v>Propuesta técnica para sincronización del caso §3.3.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="76" customHeight="1">
       <x:c r="A48" s="4" t="str">
-        <x:v>HU-47</x:v>
+        <x:v>HU-42</x:v>
       </x:c>
       <x:c r="B48" s="4" t="str">
-        <x:v>EP-07</x:v>
+        <x:v>EP-05</x:v>
       </x:c>
       <x:c r="C48" s="5" t="str">
-        <x:v>Identificar trabajo exterior</x:v>
+        <x:v>Sincronizar fotos pendientes</x:v>
       </x:c>
       <x:c r="D48" s="5" t="str">
-        <x:v>Planificador</x:v>
+        <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E48" s="5" t="str">
-        <x:v>marcar si el equipo está expuesto al clima</x:v>
+        <x:v>enviar fotos cuando vuelva la conexión</x:v>
       </x:c>
       <x:c r="F48" s="5" t="str">
-        <x:v>aplicar alertas solo donde corresponde</x:v>
+        <x:v>completar la evidencia de la intervención</x:v>
       </x:c>
       <x:c r="G48" s="4" t="str">
-        <x:v>Media</x:v>
+        <x:v>Alta</x:v>
       </x:c>
       <x:c r="H48" s="4" t="str">
         <x:v>S3 (propuesto)</x:v>
       </x:c>
       <x:c r="I48" s="4" t="str">
-        <x:v>La ficha del equipo indica si es exterior; una OT interior no muestra alertas climáticas.</x:v>
+        <x:v>Las fotos pendientes se envían por separado; su estado es visible y un fallo no elimina el archivo local.</x:v>
       </x:c>
       <x:c r="J48" s="4" t="str">
         <x:v>Lista</x:v>
@@ -3612,39 +3656,39 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M48" s="5" t="str">
-        <x:v>Propuesta para caso §3.4.</x:v>
+        <x:v>Caso §3.3; estrategia de envío propuesta.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="76" customHeight="1">
       <x:c r="A49" s="4" t="str">
-        <x:v>HU-48</x:v>
+        <x:v>HU-17</x:v>
       </x:c>
       <x:c r="B49" s="4" t="str">
-        <x:v>EP-07</x:v>
+        <x:v>EP-05</x:v>
       </x:c>
       <x:c r="C49" s="5" t="str">
-        <x:v>Ver vigencia del pronóstico</x:v>
+        <x:v>Ver estado de sincronización</x:v>
       </x:c>
       <x:c r="D49" s="5" t="str">
-        <x:v>Planificador</x:v>
+        <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E49" s="5" t="str">
-        <x:v>conocer fuente y hora de actualización del clima</x:v>
+        <x:v>distinguir registros pendientes, enviados y con error</x:v>
       </x:c>
       <x:c r="F49" s="5" t="str">
-        <x:v>valorar la confianza del aviso</x:v>
+        <x:v>saber si la información llegó</x:v>
       </x:c>
       <x:c r="G49" s="4" t="str">
-        <x:v>Media</x:v>
+        <x:v>Alta</x:v>
       </x:c>
       <x:c r="H49" s="4" t="str">
-        <x:v>S4 (propuesto)</x:v>
+        <x:v>S3 (propuesto)</x:v>
       </x:c>
       <x:c r="I49" s="4" t="str">
-        <x:v>La alerta muestra proveedor, ubicación, fecha pronosticada y hora de consulta; advierte dato no disponible.</x:v>
+        <x:v>La app indica estado por registro; un error conserva datos locales y ofrece reintento.</x:v>
       </x:c>
       <x:c r="J49" s="4" t="str">
-        <x:v>En análisis</x:v>
+        <x:v>Lista</x:v>
       </x:c>
       <x:c r="K49" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -3653,39 +3697,39 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M49" s="5" t="str">
-        <x:v>Caso §3.4. Proveedor por seleccionar.</x:v>
+        <x:v>Propuesta de usabilidad en docs/planificacion-acis.md.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="76" customHeight="1">
       <x:c r="A50" s="4" t="str">
-        <x:v>HU-49</x:v>
+        <x:v>HU-32</x:v>
       </x:c>
       <x:c r="B50" s="4" t="str">
-        <x:v>EP-07</x:v>
+        <x:v>EP-03</x:v>
       </x:c>
       <x:c r="C50" s="5" t="str">
-        <x:v>Alertar al técnico</x:v>
+        <x:v>Ver estado operativo de OT</x:v>
       </x:c>
       <x:c r="D50" s="5" t="str">
-        <x:v>Técnico</x:v>
+        <x:v>Planificador</x:v>
       </x:c>
       <x:c r="E50" s="5" t="str">
-        <x:v>ver alerta climática en una OT exterior asignada</x:v>
+        <x:v>consultar el estado actual de cada OT</x:v>
       </x:c>
       <x:c r="F50" s="5" t="str">
-        <x:v>preparar la visita con seguridad</x:v>
+        <x:v>supervisar avance</x:v>
       </x:c>
       <x:c r="G50" s="4" t="str">
-        <x:v>Media</x:v>
+        <x:v>Alta</x:v>
       </x:c>
       <x:c r="H50" s="4" t="str">
-        <x:v>S4 (propuesto)</x:v>
+        <x:v>S3 (propuesto)</x:v>
       </x:c>
       <x:c r="I50" s="4" t="str">
-        <x:v>Antes de iniciar la visita se muestra aviso vigente de lluvia o viento; no oculta la OT si falla el servicio.</x:v>
+        <x:v>La OT muestra un estado único y su historial. Solo se permiten transiciones definidas por rol: creada → asignada → aceptada → en visita → pendiente de conformidad → cerrada. Reprogramada, cancelada y visita no ejecutada conservan motivo y responsable. Un cambio local pendiente no aparece como confirmado remotamente.</x:v>
       </x:c>
       <x:c r="J50" s="4" t="str">
-        <x:v>En análisis</x:v>
+        <x:v>Lista</x:v>
       </x:c>
       <x:c r="K50" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -3694,39 +3738,39 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M50" s="5" t="str">
-        <x:v>Caso §3.4 menciona jefatura y técnico.</x:v>
+        <x:v>Caso §2.4. Estados detallados propuestos.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="76" customHeight="1">
       <x:c r="A51" s="4" t="str">
-        <x:v>HU-50</x:v>
+        <x:v>HU-58</x:v>
       </x:c>
       <x:c r="B51" s="4" t="str">
-        <x:v>EP-07</x:v>
+        <x:v>EP-09</x:v>
       </x:c>
       <x:c r="C51" s="5" t="str">
-        <x:v>Revisar alerta al reprogramar</x:v>
+        <x:v>Restringir acceso a fotos</x:v>
       </x:c>
       <x:c r="D51" s="5" t="str">
-        <x:v>Planificador</x:v>
+        <x:v>Cliente</x:v>
       </x:c>
       <x:c r="E51" s="5" t="str">
-        <x:v>actualizar el pronóstico para una nueva fecha</x:v>
+        <x:v>ver solo evidencias de mis locales</x:v>
       </x:c>
       <x:c r="F51" s="5" t="str">
-        <x:v>elegir un momento más seguro</x:v>
+        <x:v>proteger datos de otros clientes</x:v>
       </x:c>
       <x:c r="G51" s="4" t="str">
-        <x:v>Media</x:v>
+        <x:v>Alta</x:v>
       </x:c>
       <x:c r="H51" s="4" t="str">
-        <x:v>S5 (propuesto)</x:v>
+        <x:v>S4 (propuesto)</x:v>
       </x:c>
       <x:c r="I51" s="4" t="str">
-        <x:v>Al cambiar fecha de una OT exterior se consulta el pronóstico de la nueva fecha y se conserva el motivo del cambio.</x:v>
+        <x:v>Solo perfiles vinculados con el cliente o la OT acceden a sus fotos; una URL directa de otra OT también se rechaza.</x:v>
       </x:c>
       <x:c r="J51" s="4" t="str">
-        <x:v>En análisis</x:v>
+        <x:v>Lista</x:v>
       </x:c>
       <x:c r="K51" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -3735,27 +3779,27 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M51" s="5" t="str">
-        <x:v>Propuesta. Definir ventana y umbrales.</x:v>
+        <x:v>Caso §5.1. Reglas de autorización propuestas.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="76" customHeight="1">
       <x:c r="A52" s="4" t="str">
-        <x:v>HU-51</x:v>
+        <x:v>HU-41</x:v>
       </x:c>
       <x:c r="B52" s="4" t="str">
-        <x:v>EP-08</x:v>
+        <x:v>EP-05</x:v>
       </x:c>
       <x:c r="C52" s="5" t="str">
-        <x:v>Configurar política SLA</x:v>
+        <x:v>Resolver conflicto de OT</x:v>
       </x:c>
       <x:c r="D52" s="5" t="str">
-        <x:v>Jefatura</x:v>
+        <x:v>Planificador</x:v>
       </x:c>
       <x:c r="E52" s="5" t="str">
-        <x:v>registrar plazos contratados por cliente</x:v>
+        <x:v>ver cambios incompatibles hechos sin conexión</x:v>
       </x:c>
       <x:c r="F52" s="5" t="str">
-        <x:v>medir cumplimiento con la regla correcta</x:v>
+        <x:v>decidir el estado correcto de la OT</x:v>
       </x:c>
       <x:c r="G52" s="4" t="str">
         <x:v>Alta</x:v>
@@ -3764,7 +3808,7 @@
         <x:v>S5 (propuesto)</x:v>
       </x:c>
       <x:c r="I52" s="4" t="str">
-        <x:v>La política por cliente guarda plazos, vigencia y calendario de atención; una OT usa la versión vigente al inicio acordado.</x:v>
+        <x:v>Si una OT fue reasignada o cancelada mientras el técnico trabajó sin conexión, se conserva la intervención local y se marca conflicto para revisión del planificador. No se descarta ni sobrescribe automáticamente la evidencia.</x:v>
       </x:c>
       <x:c r="J52" s="4" t="str">
         <x:v>En análisis</x:v>
@@ -3776,39 +3820,39 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M52" s="5" t="str">
-        <x:v>Caso §2.3. Datos contractuales aún no entregados.</x:v>
+        <x:v>Propuesta. Falta acordar política de resolución.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="76" customHeight="1">
       <x:c r="A53" s="4" t="str">
-        <x:v>HU-52</x:v>
+        <x:v>HU-18</x:v>
       </x:c>
       <x:c r="B53" s="4" t="str">
-        <x:v>EP-08</x:v>
+        <x:v>EP-06</x:v>
       </x:c>
       <x:c r="C53" s="5" t="str">
-        <x:v>Medir tiempo de respuesta</x:v>
+        <x:v>Consultar OT propias</x:v>
       </x:c>
       <x:c r="D53" s="5" t="str">
-        <x:v>Jefatura</x:v>
+        <x:v>Cliente</x:v>
       </x:c>
       <x:c r="E53" s="5" t="str">
-        <x:v>conocer intervalo hasta la primera atención</x:v>
+        <x:v>ver el estado de las OT de mis locales</x:v>
       </x:c>
       <x:c r="F53" s="5" t="str">
-        <x:v>evaluar puntualidad inicial</x:v>
+        <x:v>seguir el servicio contratado</x:v>
       </x:c>
       <x:c r="G53" s="4" t="str">
-        <x:v>Media</x:v>
+        <x:v>Alta</x:v>
       </x:c>
       <x:c r="H53" s="4" t="str">
-        <x:v>S5 (propuesto)</x:v>
+        <x:v>S4 (propuesto)</x:v>
       </x:c>
       <x:c r="I53" s="4" t="str">
-        <x:v>El tiempo de respuesta usa el evento inicial y el primer check-in definidos en la política; muestra duración o Incompleta si falta un evento.</x:v>
+        <x:v>Solo aparecen OT de locales autorizados; cada una muestra estado, equipo y fecha de actualización.</x:v>
       </x:c>
       <x:c r="J53" s="4" t="str">
-        <x:v>En análisis</x:v>
+        <x:v>Lista</x:v>
       </x:c>
       <x:c r="K53" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -3817,39 +3861,39 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M53" s="5" t="str">
-        <x:v>Propuesta. Definir inicio del reloj SLA.</x:v>
+        <x:v>Caso §3.1. Alcance de permisos por cliente por definir.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="76" customHeight="1">
       <x:c r="A54" s="4" t="str">
-        <x:v>HU-53</x:v>
+        <x:v>HU-44</x:v>
       </x:c>
       <x:c r="B54" s="4" t="str">
-        <x:v>EP-08</x:v>
+        <x:v>EP-06</x:v>
       </x:c>
       <x:c r="C54" s="5" t="str">
-        <x:v>Medir tiempo de resolución</x:v>
+        <x:v>Revisar intervención recibida</x:v>
       </x:c>
       <x:c r="D54" s="5" t="str">
-        <x:v>Jefatura</x:v>
+        <x:v>Cliente</x:v>
       </x:c>
       <x:c r="E54" s="5" t="str">
-        <x:v>conocer intervalo hasta el cierre validado</x:v>
+        <x:v>ver resumen y evidencias de una OT de mi local</x:v>
       </x:c>
       <x:c r="F54" s="5" t="str">
-        <x:v>evaluar plazo de solución</x:v>
+        <x:v>evaluar la conformidad</x:v>
       </x:c>
       <x:c r="G54" s="4" t="str">
-        <x:v>Media</x:v>
+        <x:v>Alta</x:v>
       </x:c>
       <x:c r="H54" s="4" t="str">
-        <x:v>S5 (propuesto)</x:v>
+        <x:v>S4 (propuesto)</x:v>
       </x:c>
       <x:c r="I54" s="4" t="str">
-        <x:v>El tiempo de resolución usa el inicio y fin acordados, aplica calendario y pausas de la política; muestra duración o Incompleta.</x:v>
+        <x:v>El cliente autorizado abre solo intervenciones enviadas de sus locales y revisa diagnóstico, actividades, materiales y fotos confirmadas.</x:v>
       </x:c>
       <x:c r="J54" s="4" t="str">
-        <x:v>En análisis</x:v>
+        <x:v>Lista</x:v>
       </x:c>
       <x:c r="K54" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -3858,36 +3902,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M54" s="5" t="str">
-        <x:v>Propuesta. Acordar evento final y pausas.</x:v>
+        <x:v>Caso §3.1; detalle de revisión propuesto.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="76" customHeight="1">
       <x:c r="A55" s="4" t="str">
-        <x:v>HU-54</x:v>
+        <x:v>HU-19</x:v>
       </x:c>
       <x:c r="B55" s="4" t="str">
-        <x:v>EP-08</x:v>
+        <x:v>EP-06</x:v>
       </x:c>
       <x:c r="C55" s="5" t="str">
-        <x:v>Exportar reporte por cliente</x:v>
+        <x:v>Aprobar conformidad</x:v>
       </x:c>
       <x:c r="D55" s="5" t="str">
-        <x:v>Jefatura</x:v>
+        <x:v>Cliente</x:v>
       </x:c>
       <x:c r="E55" s="5" t="str">
-        <x:v>descargar indicadores y OT del período</x:v>
+        <x:v>aprobar una intervención recibida de mi local</x:v>
       </x:c>
       <x:c r="F55" s="5" t="str">
-        <x:v>compartir resultados verificables</x:v>
+        <x:v>validar el servicio realizado</x:v>
       </x:c>
       <x:c r="G55" s="4" t="str">
-        <x:v>Media</x:v>
+        <x:v>Alta</x:v>
       </x:c>
       <x:c r="H55" s="4" t="str">
-        <x:v>S6 (propuesto)</x:v>
+        <x:v>S4 (propuesto)</x:v>
       </x:c>
       <x:c r="I55" s="4" t="str">
-        <x:v>El reporte exportado indica cliente, período, política, OT incluidas y excluidas, tiempos, resultado SLA y fecha de generación.</x:v>
+        <x:v>Solo el cliente autorizado puede aprobar una intervención enviada; se registran usuario y fecha y la OT queda lista para cierre.</x:v>
       </x:c>
       <x:c r="J55" s="4" t="str">
         <x:v>Lista</x:v>
@@ -3899,36 +3943,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M55" s="5" t="str">
-        <x:v>Propuesta para reportes del caso §2.4 y §4.1.</x:v>
+        <x:v>Caso §3.1. Observaciones separadas en HU-68.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="76" customHeight="1">
       <x:c r="A56" s="4" t="str">
-        <x:v>HU-55</x:v>
+        <x:v>HU-68</x:v>
       </x:c>
       <x:c r="B56" s="4" t="str">
-        <x:v>EP-09</x:v>
+        <x:v>EP-06</x:v>
       </x:c>
       <x:c r="C56" s="5" t="str">
-        <x:v>Historial de eventos offline</x:v>
+        <x:v>Registrar observaciones</x:v>
       </x:c>
       <x:c r="D56" s="5" t="str">
-        <x:v>Planificador</x:v>
+        <x:v>Cliente</x:v>
       </x:c>
       <x:c r="E56" s="5" t="str">
-        <x:v>ver eventos registrados sin señal en orden correcto</x:v>
+        <x:v>dejar observaciones sobre una intervención recibida</x:v>
       </x:c>
       <x:c r="F56" s="5" t="str">
-        <x:v>reconstruir la visita</x:v>
+        <x:v>solicitar revisión antes de aprobar</x:v>
       </x:c>
       <x:c r="G56" s="4" t="str">
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="H56" s="4" t="str">
-        <x:v>S5 (propuesto)</x:v>
+        <x:v>S4 (propuesto)</x:v>
       </x:c>
       <x:c r="I56" s="4" t="str">
-        <x:v>El historial distingue hora local y recepción del servidor y conserva autor, OT y tipo de evento.</x:v>
+        <x:v>El comentario es obligatorio al observar; se guardan autor y fecha y la OT no pasa a Cerrada mientras esté pendiente.</x:v>
       </x:c>
       <x:c r="J56" s="4" t="str">
         <x:v>Lista</x:v>
@@ -3940,39 +3984,39 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M56" s="5" t="str">
-        <x:v>Caso §2.3; detalle propuesto.</x:v>
+        <x:v>Caso §3.1. Separada de HU-19.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="76" customHeight="1">
       <x:c r="A57" s="4" t="str">
-        <x:v>HU-56</x:v>
+        <x:v>HU-45</x:v>
       </x:c>
       <x:c r="B57" s="4" t="str">
-        <x:v>EP-09</x:v>
+        <x:v>EP-06</x:v>
       </x:c>
       <x:c r="C57" s="5" t="str">
-        <x:v>Auditar correcciones</x:v>
+        <x:v>Responder observaciones</x:v>
       </x:c>
       <x:c r="D57" s="5" t="str">
-        <x:v>Jefatura</x:v>
+        <x:v>Técnico</x:v>
       </x:c>
       <x:c r="E57" s="5" t="str">
-        <x:v>conocer valores anteriores y motivo de una corrección</x:v>
+        <x:v>ver observaciones del cliente y registrar respuesta</x:v>
       </x:c>
       <x:c r="F57" s="5" t="str">
-        <x:v>explicar cambios en reportes</x:v>
+        <x:v>resolver lo pendiente antes del cierre</x:v>
       </x:c>
       <x:c r="G57" s="4" t="str">
         <x:v>Media</x:v>
       </x:c>
       <x:c r="H57" s="4" t="str">
-        <x:v>S6 (propuesto)</x:v>
+        <x:v>S5 (propuesto)</x:v>
       </x:c>
       <x:c r="I57" s="4" t="str">
-        <x:v>Una corrección guarda actor, fecha, motivo y valor previo; no sobrescribe el evento histórico.</x:v>
+        <x:v>Una OT observada muestra comentario, autor y fecha; el técnico responde y la nueva revisión vuelve a Pendiente de conformidad.</x:v>
       </x:c>
       <x:c r="J57" s="4" t="str">
-        <x:v>Lista</x:v>
+        <x:v>En análisis</x:v>
       </x:c>
       <x:c r="K57" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -3981,39 +4025,39 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M57" s="5" t="str">
-        <x:v>Propuesta de auditoría para datos verificables.</x:v>
+        <x:v>Propuesta. Definir si exige nueva visita.</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="76" customHeight="1">
       <x:c r="A58" s="4" t="str">
-        <x:v>HU-57</x:v>
+        <x:v>HU-46</x:v>
       </x:c>
       <x:c r="B58" s="4" t="str">
-        <x:v>EP-09</x:v>
+        <x:v>EP-06</x:v>
       </x:c>
       <x:c r="C58" s="5" t="str">
-        <x:v>Solicitar permiso de ubicación</x:v>
+        <x:v>Cerrar OT conforme</x:v>
       </x:c>
       <x:c r="D58" s="5" t="str">
-        <x:v>Técnico</x:v>
+        <x:v>Planificador</x:v>
       </x:c>
       <x:c r="E58" s="5" t="str">
-        <x:v>autorizar ubicación solo al marcar visita</x:v>
+        <x:v>cerrar una OT tras la conformidad del cliente</x:v>
       </x:c>
       <x:c r="F58" s="5" t="str">
-        <x:v>controlar cuándo se registra mi posición</x:v>
+        <x:v>completar el ciclo verificablemente</x:v>
       </x:c>
       <x:c r="G58" s="4" t="str">
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="H58" s="4" t="str">
-        <x:v>S3 (propuesto)</x:v>
+        <x:v>S5 (propuesto)</x:v>
       </x:c>
       <x:c r="I58" s="4" t="str">
-        <x:v>La ubicación se solicita solo al hacer check-in o check-out; si se deniega, no se guarda posición y se aplica la regla de registro acordada.</x:v>
+        <x:v>Solo una OT recibida y aprobada por el cliente pasa a cerrada. Se registra usuario y fecha de conformidad; si hay observaciones, vuelve al flujo de revisión sin perder evidencias.</x:v>
       </x:c>
       <x:c r="J58" s="4" t="str">
-        <x:v>En análisis</x:v>
+        <x:v>Lista</x:v>
       </x:c>
       <x:c r="K58" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -4022,36 +4066,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M58" s="5" t="str">
-        <x:v>Caso §5.1. Definir si ubicación es obligatoria.</x:v>
+        <x:v>Regla de flujo propuesta desde caso §3.1.</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="76" customHeight="1">
       <x:c r="A59" s="4" t="str">
-        <x:v>HU-58</x:v>
+        <x:v>HU-23</x:v>
       </x:c>
       <x:c r="B59" s="4" t="str">
         <x:v>EP-09</x:v>
       </x:c>
       <x:c r="C59" s="5" t="str">
-        <x:v>Restringir acceso a fotos</x:v>
+        <x:v>Ver historial de OT</x:v>
       </x:c>
       <x:c r="D59" s="5" t="str">
-        <x:v>Cliente</x:v>
+        <x:v>Planificador</x:v>
       </x:c>
       <x:c r="E59" s="5" t="str">
-        <x:v>ver solo evidencias de mis locales</x:v>
+        <x:v>consultar eventos y responsables de cada OT</x:v>
       </x:c>
       <x:c r="F59" s="5" t="str">
-        <x:v>proteger datos de otros clientes</x:v>
+        <x:v>reconstruir el ciclo completo</x:v>
       </x:c>
       <x:c r="G59" s="4" t="str">
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="H59" s="4" t="str">
-        <x:v>S4 (propuesto)</x:v>
+        <x:v>S3 (propuesto)</x:v>
       </x:c>
       <x:c r="I59" s="4" t="str">
-        <x:v>Solo perfiles vinculados con el cliente o la OT acceden a sus fotos; una URL directa de otra OT también se rechaza.</x:v>
+        <x:v>El historial presenta creación, asignación, aceptación, visitas, conformidad y cierre en orden, con actor y fecha de cada evento.</x:v>
       </x:c>
       <x:c r="J59" s="4" t="str">
         <x:v>Lista</x:v>
@@ -4063,27 +4107,27 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M59" s="5" t="str">
-        <x:v>Caso §5.1. Reglas de autorización propuestas.</x:v>
+        <x:v>Propuesta para trazabilidad exigida por caso §2.3.</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="76" customHeight="1">
       <x:c r="A60" s="4" t="str">
-        <x:v>HU-59</x:v>
+        <x:v>HU-55</x:v>
       </x:c>
       <x:c r="B60" s="4" t="str">
         <x:v>EP-09</x:v>
       </x:c>
       <x:c r="C60" s="5" t="str">
-        <x:v>Proteger datos locales</x:v>
+        <x:v>Historial de eventos offline</x:v>
       </x:c>
       <x:c r="D60" s="5" t="str">
-        <x:v>Técnico</x:v>
+        <x:v>Planificador</x:v>
       </x:c>
       <x:c r="E60" s="5" t="str">
-        <x:v>mantener protegidos los registros guardados en el teléfono</x:v>
+        <x:v>ver eventos registrados sin señal en orden correcto</x:v>
       </x:c>
       <x:c r="F60" s="5" t="str">
-        <x:v>evitar acceso indebido si pierdo el dispositivo</x:v>
+        <x:v>reconstruir la visita</x:v>
       </x:c>
       <x:c r="G60" s="4" t="str">
         <x:v>Alta</x:v>
@@ -4092,10 +4136,10 @@
         <x:v>S5 (propuesto)</x:v>
       </x:c>
       <x:c r="I60" s="4" t="str">
-        <x:v>Datos y fotos locales no aparecen en otras cuentas; cerrar sesión impide consultar OT descargadas sin volver a autenticarse.</x:v>
+        <x:v>El historial distingue hora local y recepción del servidor y conserva autor, OT y tipo de evento.</x:v>
       </x:c>
       <x:c r="J60" s="4" t="str">
-        <x:v>En análisis</x:v>
+        <x:v>Lista</x:v>
       </x:c>
       <x:c r="K60" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -4104,27 +4148,27 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M60" s="5" t="str">
-        <x:v>Propuesta. Definir cifrado y política de borrado local.</x:v>
+        <x:v>Caso §2.3; detalle propuesto.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="76" customHeight="1">
       <x:c r="A61" s="4" t="str">
-        <x:v>HU-60</x:v>
+        <x:v>HU-56</x:v>
       </x:c>
       <x:c r="B61" s="4" t="str">
         <x:v>EP-09</x:v>
       </x:c>
       <x:c r="C61" s="5" t="str">
-        <x:v>Gestionar retención de evidencias</x:v>
+        <x:v>Auditar correcciones</x:v>
       </x:c>
       <x:c r="D61" s="5" t="str">
         <x:v>Jefatura</x:v>
       </x:c>
       <x:c r="E61" s="5" t="str">
-        <x:v>aplicar un plazo de conservación aprobado</x:v>
+        <x:v>conocer valores anteriores y motivo de una corrección</x:v>
       </x:c>
       <x:c r="F61" s="5" t="str">
-        <x:v>cumplir la política de datos personales</x:v>
+        <x:v>explicar cambios en reportes</x:v>
       </x:c>
       <x:c r="G61" s="4" t="str">
         <x:v>Media</x:v>
@@ -4133,10 +4177,10 @@
         <x:v>S6 (propuesto)</x:v>
       </x:c>
       <x:c r="I61" s="4" t="str">
-        <x:v>La política define plazo y tratamiento al vencer; eliminación o anonimización queda registrada y no rompe la OT.</x:v>
+        <x:v>Una corrección guarda actor, fecha, motivo y valor previo; no sobrescribe el evento histórico.</x:v>
       </x:c>
       <x:c r="J61" s="4" t="str">
-        <x:v>En análisis</x:v>
+        <x:v>Lista</x:v>
       </x:c>
       <x:c r="K61" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -4145,39 +4189,39 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M61" s="5" t="str">
-        <x:v>Caso §5.1. Plazo y normativa específica por confirmar.</x:v>
+        <x:v>Propuesta de auditoría para datos verificables.</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="76" customHeight="1">
       <x:c r="A62" s="4" t="str">
-        <x:v>HU-61</x:v>
+        <x:v>HU-21</x:v>
       </x:c>
       <x:c r="B62" s="4" t="str">
-        <x:v>EP-02</x:v>
+        <x:v>EP-08</x:v>
       </x:c>
       <x:c r="C62" s="5" t="str">
-        <x:v>Registrar local</x:v>
+        <x:v>Consultar duración de atención</x:v>
       </x:c>
       <x:c r="D62" s="5" t="str">
-        <x:v>Planificador</x:v>
+        <x:v>Jefatura</x:v>
       </x:c>
       <x:c r="E62" s="5" t="str">
-        <x:v>crear un local para un cliente</x:v>
+        <x:v>ver duración de visitas por OT y cliente</x:v>
       </x:c>
       <x:c r="F62" s="5" t="str">
-        <x:v>ubicar correctamente sus equipos y OT</x:v>
+        <x:v>evaluar tiempos reales de ejecución</x:v>
       </x:c>
       <x:c r="G62" s="4" t="str">
-        <x:v>Alta</x:v>
+        <x:v>Media</x:v>
       </x:c>
       <x:c r="H62" s="4" t="str">
-        <x:v>S2 (propuesto)</x:v>
+        <x:v>S4 (propuesto)</x:v>
       </x:c>
       <x:c r="I62" s="4" t="str">
-        <x:v>El local exige cliente existente, nombre y dirección; aparece en la ficha del cliente y puede contener equipos.</x:v>
+        <x:v>El reporte calcula tiempo entre check-in y check-out de cada visita, muestra período y marca incompleta la visita sin ambos eventos.</x:v>
       </x:c>
       <x:c r="J62" s="4" t="str">
-        <x:v>Lista</x:v>
+        <x:v>En análisis</x:v>
       </x:c>
       <x:c r="K62" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -4186,36 +4230,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M62" s="5" t="str">
-        <x:v>Caso §3.2. Separa cliente y local, antes combinados en HU-02.</x:v>
+        <x:v>Caso §2.3, §4.1. Diferente de tiempo de respuesta SLA en HU-52.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="76" customHeight="1">
       <x:c r="A63" s="4" t="str">
-        <x:v>HU-62</x:v>
+        <x:v>HU-51</x:v>
       </x:c>
       <x:c r="B63" s="4" t="str">
-        <x:v>EP-01</x:v>
+        <x:v>EP-08</x:v>
       </x:c>
       <x:c r="C63" s="5" t="str">
-        <x:v>Administrar cuentas del equipo</x:v>
+        <x:v>Configurar política SLA</x:v>
       </x:c>
       <x:c r="D63" s="5" t="str">
         <x:v>Jefatura</x:v>
       </x:c>
       <x:c r="E63" s="5" t="str">
-        <x:v>activar o desactivar cuentas de técnicos y planificadores</x:v>
+        <x:v>registrar plazos contratados por cliente</x:v>
       </x:c>
       <x:c r="F63" s="5" t="str">
-        <x:v>controlar quién opera el sistema</x:v>
+        <x:v>medir cumplimiento con la regla correcta</x:v>
       </x:c>
       <x:c r="G63" s="4" t="str">
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="H63" s="4" t="str">
-        <x:v>S2 (propuesto)</x:v>
+        <x:v>S5 (propuesto)</x:v>
       </x:c>
       <x:c r="I63" s="4" t="str">
-        <x:v>Se registra perfil y estado de la cuenta; una cuenta inactiva no inicia sesión ni recibe nuevas OT.</x:v>
+        <x:v>La política por cliente guarda plazos, vigencia y calendario de atención; una OT usa la versión vigente al inicio acordado.</x:v>
       </x:c>
       <x:c r="J63" s="4" t="str">
         <x:v>En análisis</x:v>
@@ -4227,36 +4271,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M63" s="5" t="str">
-        <x:v>Propuesta necesaria para perfiles del caso §3.1; definir autoridad de administración.</x:v>
+        <x:v>Caso §2.3. Datos contractuales aún no entregados.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="76" customHeight="1">
       <x:c r="A64" s="4" t="str">
-        <x:v>HU-63</x:v>
+        <x:v>HU-52</x:v>
       </x:c>
       <x:c r="B64" s="4" t="str">
-        <x:v>EP-01</x:v>
+        <x:v>EP-08</x:v>
       </x:c>
       <x:c r="C64" s="5" t="str">
-        <x:v>Asociar cliente a locales</x:v>
+        <x:v>Medir tiempo de respuesta</x:v>
       </x:c>
       <x:c r="D64" s="5" t="str">
         <x:v>Jefatura</x:v>
       </x:c>
       <x:c r="E64" s="5" t="str">
-        <x:v>asignar a un usuario cliente sus locales autorizados</x:v>
+        <x:v>conocer intervalo hasta la primera atención</x:v>
       </x:c>
       <x:c r="F64" s="5" t="str">
-        <x:v>delimitar qué OT puede consultar</x:v>
+        <x:v>evaluar puntualidad inicial</x:v>
       </x:c>
       <x:c r="G64" s="4" t="str">
-        <x:v>Alta</x:v>
+        <x:v>Media</x:v>
       </x:c>
       <x:c r="H64" s="4" t="str">
-        <x:v>S3 (propuesto)</x:v>
+        <x:v>S5 (propuesto)</x:v>
       </x:c>
       <x:c r="I64" s="4" t="str">
-        <x:v>Un cliente ve solo OT de locales asociados; al quitar una asociación pierde acceso a esas OT y evidencias.</x:v>
+        <x:v>El tiempo de respuesta usa el evento inicial y el primer check-in definidos en la política; muestra duración o Incompleta si falta un evento.</x:v>
       </x:c>
       <x:c r="J64" s="4" t="str">
         <x:v>En análisis</x:v>
@@ -4268,39 +4312,39 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M64" s="5" t="str">
-        <x:v>Propuesta de autorización a partir del caso §3.1.</x:v>
+        <x:v>Propuesta. Definir inicio del reloj SLA.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="76" customHeight="1">
       <x:c r="A65" s="4" t="str">
-        <x:v>HU-64</x:v>
+        <x:v>HU-53</x:v>
       </x:c>
       <x:c r="B65" s="4" t="str">
-        <x:v>EP-01</x:v>
+        <x:v>EP-08</x:v>
       </x:c>
       <x:c r="C65" s="5" t="str">
-        <x:v>Cerrar sesión</x:v>
+        <x:v>Medir tiempo de resolución</x:v>
       </x:c>
       <x:c r="D65" s="5" t="str">
-        <x:v>Usuario de ACIS</x:v>
+        <x:v>Jefatura</x:v>
       </x:c>
       <x:c r="E65" s="5" t="str">
-        <x:v>cerrar mi sesión en el teléfono</x:v>
+        <x:v>conocer intervalo hasta el cierre validado</x:v>
       </x:c>
       <x:c r="F65" s="5" t="str">
-        <x:v>impedir uso de mi cuenta por otra persona</x:v>
+        <x:v>evaluar plazo de solución</x:v>
       </x:c>
       <x:c r="G65" s="4" t="str">
-        <x:v>Alta</x:v>
+        <x:v>Media</x:v>
       </x:c>
       <x:c r="H65" s="4" t="str">
-        <x:v>S2 (propuesto)</x:v>
+        <x:v>S5 (propuesto)</x:v>
       </x:c>
       <x:c r="I65" s="4" t="str">
-        <x:v>Al cerrar sesión se vuelve a acceso y no se muestran OT ni fotos locales sin nueva autenticación.</x:v>
+        <x:v>El tiempo de resolución usa el inicio y fin acordados, aplica calendario y pausas de la política; muestra duración o Incompleta.</x:v>
       </x:c>
       <x:c r="J65" s="4" t="str">
-        <x:v>Lista</x:v>
+        <x:v>En análisis</x:v>
       </x:c>
       <x:c r="K65" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -4309,36 +4353,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M65" s="5" t="str">
-        <x:v>Propuesta complementaria a privacidad del caso §5.1.</x:v>
+        <x:v>Propuesta. Acordar evento final y pausas.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="76" customHeight="1">
       <x:c r="A66" s="4" t="str">
-        <x:v>HU-65</x:v>
+        <x:v>HU-22</x:v>
       </x:c>
       <x:c r="B66" s="4" t="str">
-        <x:v>EP-03</x:v>
+        <x:v>EP-08</x:v>
       </x:c>
       <x:c r="C66" s="5" t="str">
-        <x:v>Cancelar OT</x:v>
+        <x:v>Consultar cumplimiento SLA</x:v>
       </x:c>
       <x:c r="D66" s="5" t="str">
-        <x:v>Planificador</x:v>
+        <x:v>Jefatura</x:v>
       </x:c>
       <x:c r="E66" s="5" t="str">
-        <x:v>cancelar una visita que ya no se realizará</x:v>
+        <x:v>ver OT dentro o fuera del plazo contratado</x:v>
       </x:c>
       <x:c r="F66" s="5" t="str">
-        <x:v>evitar que el técnico la ejecute</x:v>
+        <x:v>reportar servicio por cliente</x:v>
       </x:c>
       <x:c r="G66" s="4" t="str">
         <x:v>Media</x:v>
       </x:c>
       <x:c r="H66" s="4" t="str">
-        <x:v>S4 (propuesto)</x:v>
+        <x:v>S5 (propuesto)</x:v>
       </x:c>
       <x:c r="I66" s="4" t="str">
-        <x:v>Cancelar exige motivo; la OT queda Cancelada, no admite nuevo check-in y el técnico ve el cambio al sincronizar.</x:v>
+        <x:v>Para cada OT se muestra la política SLA aplicable, plazo, resultado y causa de exclusión; las OT sin datos suficientes figuran incompletas.</x:v>
       </x:c>
       <x:c r="J66" s="4" t="str">
         <x:v>En análisis</x:v>
@@ -4350,36 +4394,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M66" s="5" t="str">
-        <x:v>Propuesta. Definir resolución si el técnico ya inició offline.</x:v>
+        <x:v>Caso §2.3, §4.1. Regla contractual pendiente; cálculo detallado en HU-52 y HU-53.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="76" customHeight="1">
       <x:c r="A67" s="4" t="str">
-        <x:v>HU-66</x:v>
+        <x:v>HU-54</x:v>
       </x:c>
       <x:c r="B67" s="4" t="str">
-        <x:v>EP-04</x:v>
+        <x:v>EP-08</x:v>
       </x:c>
       <x:c r="C67" s="5" t="str">
-        <x:v>Registrar check-out</x:v>
+        <x:v>Exportar reporte por cliente</x:v>
       </x:c>
       <x:c r="D67" s="5" t="str">
-        <x:v>Técnico</x:v>
+        <x:v>Jefatura</x:v>
       </x:c>
       <x:c r="E67" s="5" t="str">
-        <x:v>marcar mi salida del local</x:v>
+        <x:v>descargar indicadores y OT del período</x:v>
       </x:c>
       <x:c r="F67" s="5" t="str">
-        <x:v>cerrar el tiempo de la visita</x:v>
+        <x:v>compartir resultados verificables</x:v>
       </x:c>
       <x:c r="G67" s="4" t="str">
-        <x:v>Alta</x:v>
+        <x:v>Media</x:v>
       </x:c>
       <x:c r="H67" s="4" t="str">
-        <x:v>S2 (propuesto)</x:v>
+        <x:v>S6 (propuesto)</x:v>
       </x:c>
       <x:c r="I67" s="4" t="str">
-        <x:v>Se registra fecha y hora incluso sin señal; requiere check-in previo de la misma visita y no acepta hora anterior.</x:v>
+        <x:v>El reporte exportado indica cliente, período, política, OT incluidas y excluidas, tiempos, resultado SLA y fecha de generación.</x:v>
       </x:c>
       <x:c r="J67" s="4" t="str">
         <x:v>Lista</x:v>
@@ -4391,36 +4435,36 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M67" s="5" t="str">
-        <x:v>Caso §3.3. Separada de HU-10 para aceptación independiente.</x:v>
+        <x:v>Propuesta para reportes del caso §2.4 y §4.1.</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="76" customHeight="1">
       <x:c r="A68" s="4" t="str">
-        <x:v>HU-67</x:v>
+        <x:v>HU-28</x:v>
       </x:c>
       <x:c r="B68" s="4" t="str">
-        <x:v>EP-04</x:v>
+        <x:v>EP-03</x:v>
       </x:c>
       <x:c r="C68" s="5" t="str">
-        <x:v>Registrar materiales usados</x:v>
+        <x:v>Buscar y filtrar OT</x:v>
       </x:c>
       <x:c r="D68" s="5" t="str">
-        <x:v>Técnico</x:v>
+        <x:v>Planificador</x:v>
       </x:c>
       <x:c r="E68" s="5" t="str">
-        <x:v>anotar materiales y cantidades de la intervención</x:v>
+        <x:v>filtrar OT por estado, cliente y fecha</x:v>
       </x:c>
       <x:c r="F68" s="5" t="str">
-        <x:v>dejar trazabilidad de lo consumido</x:v>
+        <x:v>ubicar trabajos que requieren atención</x:v>
       </x:c>
       <x:c r="G68" s="4" t="str">
-        <x:v>Alta</x:v>
+        <x:v>Media</x:v>
       </x:c>
       <x:c r="H68" s="4" t="str">
-        <x:v>S2 (propuesto)</x:v>
+        <x:v>S3 (propuesto)</x:v>
       </x:c>
       <x:c r="I68" s="4" t="str">
-        <x:v>Cada material incluye nombre o código, cantidad positiva y unidad; puede guardarse sin conexión y editarse en borrador.</x:v>
+        <x:v>Los filtros se combinan; la lista indica filtros activos y permite volver a todas las OT.</x:v>
       </x:c>
       <x:c r="J68" s="4" t="str">
         <x:v>Lista</x:v>
@@ -4432,39 +4476,39 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M68" s="5" t="str">
-        <x:v>Caso §3.2. Separada de HU-12.</x:v>
+        <x:v>Propuesta para supervisión del caso §2.4.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="76" customHeight="1">
       <x:c r="A69" s="4" t="str">
-        <x:v>HU-68</x:v>
+        <x:v>HU-60</x:v>
       </x:c>
       <x:c r="B69" s="4" t="str">
-        <x:v>EP-06</x:v>
+        <x:v>EP-09</x:v>
       </x:c>
       <x:c r="C69" s="5" t="str">
-        <x:v>Registrar observaciones</x:v>
+        <x:v>Gestionar retención de evidencias</x:v>
       </x:c>
       <x:c r="D69" s="5" t="str">
-        <x:v>Cliente</x:v>
+        <x:v>Jefatura</x:v>
       </x:c>
       <x:c r="E69" s="5" t="str">
-        <x:v>dejar observaciones sobre una intervención recibida</x:v>
+        <x:v>aplicar un plazo de conservación aprobado</x:v>
       </x:c>
       <x:c r="F69" s="5" t="str">
-        <x:v>solicitar revisión antes de aprobar</x:v>
+        <x:v>cumplir la política de datos personales</x:v>
       </x:c>
       <x:c r="G69" s="4" t="str">
-        <x:v>Alta</x:v>
+        <x:v>Media</x:v>
       </x:c>
       <x:c r="H69" s="4" t="str">
-        <x:v>S4 (propuesto)</x:v>
+        <x:v>S6 (propuesto)</x:v>
       </x:c>
       <x:c r="I69" s="4" t="str">
-        <x:v>El comentario es obligatorio al observar; se guardan autor y fecha y la OT no pasa a Cerrada mientras esté pendiente.</x:v>
+        <x:v>La política define plazo y tratamiento al vencer; eliminación o anonimización queda registrada y no rompe la OT.</x:v>
       </x:c>
       <x:c r="J69" s="4" t="str">
-        <x:v>Lista</x:v>
+        <x:v>En análisis</x:v>
       </x:c>
       <x:c r="K69" s="4" t="str">
         <x:v>Pendiente</x:v>
@@ -4473,38 +4517,86 @@
         <x:v>Equipo de desarrollo</x:v>
       </x:c>
       <x:c r="M69" s="5" t="str">
-        <x:v>Caso §3.1. Separada de HU-19.</x:v>
+        <x:v>Caso §5.1. Plazo y normativa específica por confirmar.</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="33.599998474121094" customHeight="1">
-      <x:c r="A70" s="3"/>
-      <x:c r="B70" s="3"/>
-      <x:c r="C70" s="2"/>
-      <x:c r="D70" s="2"/>
-      <x:c r="E70" s="2"/>
-      <x:c r="F70" s="2"/>
-      <x:c r="G70" s="3"/>
-      <x:c r="H70" s="3"/>
-      <x:c r="I70" s="3"/>
-      <x:c r="J70" s="3"/>
-      <x:c r="K70" s="3"/>
-      <x:c r="L70" s="2"/>
-      <x:c r="M70" s="2"/>
+      <x:c r="A70" s="3" t="str">
+        <x:v>HU-69</x:v>
+      </x:c>
+      <x:c r="B70" s="3" t="str">
+        <x:v>EP-03</x:v>
+      </x:c>
+      <x:c r="C70" s="2" t="str">
+        <x:v>Consultar agenda diaria</x:v>
+      </x:c>
+      <x:c r="D70" s="2" t="str">
+        <x:v>Técnico</x:v>
+      </x:c>
+      <x:c r="E70" s="2" t="str">
+        <x:v>ver mis visitas del día ordenadas por horario</x:v>
+      </x:c>
+      <x:c r="F70" s="2" t="str">
+        <x:v>preparar la jornada y reconocer cambios de programación</x:v>
+      </x:c>
+      <x:c r="G70" s="3" t="str">
+        <x:v>Media</x:v>
+      </x:c>
+      <x:c r="H70" s="3" t="str">
+        <x:v>S3 (propuesto)</x:v>
+      </x:c>
+      <x:c r="I70" s="3" t="str">
+        <x:v>La agenda muestra hora, local, equipo y estado de cada OT asignada al técnico. Un cambio confirmado aparece al actualizar los datos; se indica si la copia local está pendiente de sincronización.</x:v>
+      </x:c>
+      <x:c r="J70" s="3" t="str">
+        <x:v>Pendiente</x:v>
+      </x:c>
+      <x:c r="K70" s="3" t="str">
+        <x:v>Pendiente</x:v>
+      </x:c>
+      <x:c r="L70" s="2" t="str"/>
+      <x:c r="M70" s="2" t="str">
+        <x:v>Nueva historia; depende de HU-05 y HU-07.</x:v>
+      </x:c>
     </x:row>
     <x:row r="71" ht="33.599998474121094" customHeight="1">
-      <x:c r="A71" s="3"/>
-      <x:c r="B71" s="3"/>
-      <x:c r="C71" s="2"/>
-      <x:c r="D71" s="2"/>
-      <x:c r="E71" s="2"/>
-      <x:c r="F71" s="2"/>
-      <x:c r="G71" s="3"/>
-      <x:c r="H71" s="3"/>
-      <x:c r="I71" s="3"/>
-      <x:c r="J71" s="3"/>
-      <x:c r="K71" s="3"/>
-      <x:c r="L71" s="2"/>
-      <x:c r="M71" s="2"/>
+      <x:c r="A71" s="3" t="str">
+        <x:v>HU-70</x:v>
+      </x:c>
+      <x:c r="B71" s="3" t="str">
+        <x:v>EP-04</x:v>
+      </x:c>
+      <x:c r="C71" s="2" t="str">
+        <x:v>Registrar visita no ejecutada</x:v>
+      </x:c>
+      <x:c r="D71" s="2" t="str">
+        <x:v>Técnico</x:v>
+      </x:c>
+      <x:c r="E71" s="2" t="str">
+        <x:v>registrar que no pude realizar una visita y su motivo</x:v>
+      </x:c>
+      <x:c r="F71" s="2" t="str">
+        <x:v>permitir su reprogramación sin inventar diagnóstico ni cierre técnico</x:v>
+      </x:c>
+      <x:c r="G71" s="3" t="str">
+        <x:v>Alta</x:v>
+      </x:c>
+      <x:c r="H71" s="3" t="str">
+        <x:v>S4 (propuesto)</x:v>
+      </x:c>
+      <x:c r="I71" s="3" t="str">
+        <x:v>Se selecciona un motivo y se guarda fecha, técnico y observación opcional. La OT queda pendiente de revisión o reprogramación, sin exigir diagnóstico ni fotos. El evento puede guardarse sin conexión y mantiene trazabilidad.</x:v>
+      </x:c>
+      <x:c r="J71" s="3" t="str">
+        <x:v>Pendiente</x:v>
+      </x:c>
+      <x:c r="K71" s="3" t="str">
+        <x:v>Pendiente</x:v>
+      </x:c>
+      <x:c r="L71" s="2" t="str"/>
+      <x:c r="M71" s="2" t="str">
+        <x:v>Nueva historia; depende de HU-05, HU-15 y HU-32.</x:v>
+      </x:c>
     </x:row>
     <x:row r="72" ht="33.599998474121094" customHeight="1">
       <x:c r="A72" s="3"/>
@@ -6500,7 +6592,1973 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f62c2353c114536"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdeaf4b3cea7d4291"/>
   </x:tableParts>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF1F4E78"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="46" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="31" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="67" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="8" t="str">
+        <x:v>Paso</x:v>
+      </x:c>
+      <x:c r="B1" s="8" t="str">
+        <x:v>Responsable</x:v>
+      </x:c>
+      <x:c r="C1" s="8" t="str">
+        <x:v>Acción</x:v>
+      </x:c>
+      <x:c r="D1" s="8" t="str">
+        <x:v>Resultado / estado</x:v>
+      </x:c>
+      <x:c r="E1" s="8" t="str">
+        <x:v>Sin conexión</x:v>
+      </x:c>
+      <x:c r="F1" s="8" t="str">
+        <x:v>Historias</x:v>
+      </x:c>
+      <x:c r="G1" s="8" t="str">
+        <x:v>Condición para avanzar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="58" customHeight="1">
+      <x:c r="A2" s="11" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="11" t="str">
+        <x:v>Planificador</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="str">
+        <x:v>Preparar cuentas, cliente, local y equipo.</x:v>
+      </x:c>
+      <x:c r="D2" s="11" t="str">
+        <x:v>Catastro y accesos disponibles</x:v>
+      </x:c>
+      <x:c r="E2" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F2" s="11" t="str">
+        <x:v>HU-62, 02, 61, 03, 63, 01</x:v>
+      </x:c>
+      <x:c r="G2" s="11" t="str">
+        <x:v>El usuario autorizado ve únicamente sus datos.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="58" customHeight="1">
+      <x:c r="A3" s="13" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="13" t="str">
+        <x:v>Planificador</x:v>
+      </x:c>
+      <x:c r="C3" s="13" t="str">
+        <x:v>Crear la OT con equipo, prioridad y fecha.</x:v>
+      </x:c>
+      <x:c r="D3" s="13" t="str">
+        <x:v>Creada</x:v>
+      </x:c>
+      <x:c r="E3" s="13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F3" s="13" t="str">
+        <x:v>HU-04</x:v>
+      </x:c>
+      <x:c r="G3" s="13" t="str">
+        <x:v>La OT tiene ID y equipo del local correcto.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="58" customHeight="1">
+      <x:c r="A4" s="11" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="str">
+        <x:v>Planificador</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="str">
+        <x:v>Revisar pronóstico si el equipo es exterior.</x:v>
+      </x:c>
+      <x:c r="D4" s="11" t="str">
+        <x:v>Alerta o dato no disponible</x:v>
+      </x:c>
+      <x:c r="E4" s="11" t="str">
+        <x:v>Requiere señal</x:v>
+      </x:c>
+      <x:c r="F4" s="11" t="str">
+        <x:v>HU-47, 20, 48</x:v>
+      </x:c>
+      <x:c r="G4" s="11" t="str">
+        <x:v>La jefatura decide fecha; una falla climática no bloquea la OT.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="58" customHeight="1">
+      <x:c r="A5" s="13" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="13" t="str">
+        <x:v>Planificador</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="str">
+        <x:v>Validar disponibilidad y asignar técnico.</x:v>
+      </x:c>
+      <x:c r="D5" s="13" t="str">
+        <x:v>Agenda del técnico disponible</x:v>
+      </x:c>
+      <x:c r="E5" s="13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F5" s="13" t="str">
+        <x:v>HU-05, HU-07, HU-69</x:v>
+      </x:c>
+      <x:c r="G5" s="13" t="str">
+        <x:v>Asignación registrada con actor y fecha.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="58" customHeight="1">
+      <x:c r="A6" s="11" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>Técnico</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>Descargar y consultar sus OT y el equipo.</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>OT preparada en el dispositivo</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>Primera descarga: no</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
+        <x:v>HU-39, 07, 08, 27</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="str">
+        <x:v>La OT y sus datos están disponibles sin señal.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="58" customHeight="1">
+      <x:c r="A7" s="13" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B7" s="13" t="str">
+        <x:v>Técnico</x:v>
+      </x:c>
+      <x:c r="C7" s="13" t="str">
+        <x:v>Aceptar la OT asignada.</x:v>
+      </x:c>
+      <x:c r="D7" s="13" t="str">
+        <x:v>Aceptada</x:v>
+      </x:c>
+      <x:c r="E7" s="13" t="str">
+        <x:v>Por definir</x:v>
+      </x:c>
+      <x:c r="F7" s="13" t="str">
+        <x:v>HU-09</x:v>
+      </x:c>
+      <x:c r="G7" s="13" t="str">
+        <x:v>Solo el técnico asignado puede aceptarla.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="58" customHeight="1">
+      <x:c r="A8" s="11" t="str">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="11" t="str">
+        <x:v>Técnico</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="str">
+        <x:v>Abrir intervención, pedir permiso de ubicación y hacer check-in.</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="str">
+        <x:v>En ejecución</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="str">
+        <x:v>Sí, con OT descargada</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="str">
+        <x:v>HU-33, 57, 10</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="str">
+        <x:v>Quedan visita y hora original registradas.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="58" customHeight="1">
+      <x:c r="A9" s="13" t="str">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" s="13" t="str">
+        <x:v>Técnico</x:v>
+      </x:c>
+      <x:c r="C9" s="13" t="str">
+        <x:v>Guardar diagnóstico, actividades y materiales en borrador.</x:v>
+      </x:c>
+      <x:c r="D9" s="13" t="str">
+        <x:v>Borrador de intervención</x:v>
+      </x:c>
+      <x:c r="E9" s="13" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="F9" s="13" t="str">
+        <x:v>HU-38, 34, 11, 12, 67</x:v>
+      </x:c>
+      <x:c r="G9" s="13" t="str">
+        <x:v>Los datos persisten al cerrar y abrir la app.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="58" customHeight="1">
+      <x:c r="A10" s="11" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B10" s="11" t="str">
+        <x:v>Técnico</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="str">
+        <x:v>Adjuntar fotos del equipo y, si aplica, antes/después.</x:v>
+      </x:c>
+      <x:c r="D10" s="11" t="str">
+        <x:v>Evidencia local pendiente</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="str">
+        <x:v>HU-13, 36</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="str">
+        <x:v>Cada foto queda ligada a la visita y se conserva hasta confirmar envío.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="58" customHeight="1">
+      <x:c r="A11" s="13" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B11" s="13" t="str">
+        <x:v>Técnico</x:v>
+      </x:c>
+      <x:c r="C11" s="13" t="str">
+        <x:v>Registrar check-out de la misma visita.</x:v>
+      </x:c>
+      <x:c r="D11" s="13" t="str">
+        <x:v>Visita terminada</x:v>
+      </x:c>
+      <x:c r="E11" s="13" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="F11" s="13" t="str">
+        <x:v>HU-66, 43</x:v>
+      </x:c>
+      <x:c r="G11" s="13" t="str">
+        <x:v>La salida es posterior a la llegada; ambas horas se conservan.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="58" customHeight="1">
+      <x:c r="A12" s="11" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B12" s="11" t="str">
+        <x:v>Técnico</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="str">
+        <x:v>Revisar resumen y enviar cierre técnico.</x:v>
+      </x:c>
+      <x:c r="D12" s="11" t="str">
+        <x:v>Pendiente de envío local</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="str">
+        <x:v>HU-37, 15, 14</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="str">
+        <x:v>Faltantes visibles; cierre local persistido antes de salir.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="58" customHeight="1">
+      <x:c r="A13" s="13" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B13" s="13" t="str">
+        <x:v>Sistema</x:v>
+      </x:c>
+      <x:c r="C13" s="13" t="str">
+        <x:v>Sincronizar eventos y fotos; reintentar sin duplicar.</x:v>
+      </x:c>
+      <x:c r="D13" s="13" t="str">
+        <x:v>Pendiente de conformidad al confirmarse</x:v>
+      </x:c>
+      <x:c r="E13" s="13" t="str">
+        <x:v>Al recuperar señal</x:v>
+      </x:c>
+      <x:c r="F13" s="13" t="str">
+        <x:v>HU-16, 40, 42, 17, 41</x:v>
+      </x:c>
+      <x:c r="G13" s="13" t="str">
+        <x:v>Servidor confirma registros y fotos; conflictos quedan retenidos para revisión.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="58" customHeight="1">
+      <x:c r="A14" s="11" t="str">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="str">
+        <x:v>Cliente</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="str">
+        <x:v>Consultar su OT y revisar intervención confirmada.</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="str">
+        <x:v>Pendiente de conformidad</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="str">
+        <x:v>HU-18, 44, 58</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="str">
+        <x:v>Solo el cliente del local accede a los datos y evidencias.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="58" customHeight="1">
+      <x:c r="A15" s="13" t="str">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B15" s="13" t="str">
+        <x:v>Cliente</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="str">
+        <x:v>Aprobar o registrar observaciones.</x:v>
+      </x:c>
+      <x:c r="D15" s="13" t="str">
+        <x:v>Conforme o con observaciones</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F15" s="13" t="str">
+        <x:v>HU-19, 68</x:v>
+      </x:c>
+      <x:c r="G15" s="13" t="str">
+        <x:v>La decisión guarda autor y fecha.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="58" customHeight="1">
+      <x:c r="A16" s="11" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B16" s="11" t="str">
+        <x:v>Técnico</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="str">
+        <x:v>Responder observaciones o realizar otra visita si corresponde.</x:v>
+      </x:c>
+      <x:c r="D16" s="11" t="str">
+        <x:v>Nueva revisión pendiente</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="str">
+        <x:v>Visita: sí</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="str">
+        <x:v>HU-45, 35</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="str">
+        <x:v>El cliente vuelve a revisar; no se cierra con observaciones abiertas.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="58" customHeight="1">
+      <x:c r="A17" s="13" t="str">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B17" s="13" t="str">
+        <x:v>Planificador</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="str">
+        <x:v>Cerrar OT con conformidad aprobada.</x:v>
+      </x:c>
+      <x:c r="D17" s="13" t="str">
+        <x:v>Cerrada</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F17" s="13" t="str">
+        <x:v>HU-46</x:v>
+      </x:c>
+      <x:c r="G17" s="13" t="str">
+        <x:v>Cierre y conformidad quedan en historial.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="58" customHeight="1">
+      <x:c r="A18" s="11" t="str">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B18" s="11" t="str">
+        <x:v>Jefatura</x:v>
+      </x:c>
+      <x:c r="C18" s="11" t="str">
+        <x:v>Consultar historial, duración y cumplimiento SLA.</x:v>
+      </x:c>
+      <x:c r="D18" s="11" t="str">
+        <x:v>Reporte verificable</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F18" s="11" t="str">
+        <x:v>HU-23, 21, 51-54, 55-56</x:v>
+      </x:c>
+      <x:c r="G18" s="11" t="str">
+        <x:v>Política y eventos completos; faltantes se indican como incompletos.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="58" customHeight="1">
+      <x:c r="A19" s="13" t="str">
+        <x:v>Alternativa</x:v>
+      </x:c>
+      <x:c r="B19" s="13" t="str">
+        <x:v>Planificador</x:v>
+      </x:c>
+      <x:c r="C19" s="13" t="str">
+        <x:v>Reprogramar o cancelar antes o durante la visita.</x:v>
+      </x:c>
+      <x:c r="D19" s="13" t="str">
+        <x:v>Reprogramada o cancelada</x:v>
+      </x:c>
+      <x:c r="E19" s="13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F19" s="13" t="str">
+        <x:v>HU-06, 31, 50, 65</x:v>
+      </x:c>
+      <x:c r="G19" s="13" t="str">
+        <x:v>Se guarda motivo y se resuelve cualquier cambio hecho sin señal.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="28" customHeight="1">
+      <x:c r="A21" s="12" t="str">
+        <x:v>Orden técnico sugerido. Sprints ajustados a las dependencias; validar capacidad y esfuerzo antes de fijarlos.</x:v>
+      </x:c>
+      <x:c r="B21" s="12"/>
+      <x:c r="C21" s="12"/>
+      <x:c r="D21" s="12"/>
+      <x:c r="E21" s="12"/>
+      <x:c r="F21" s="12"/>
+      <x:c r="G21" s="12"/>
+    </x:row>
+    <x:row r="22" ht="28" customHeight="1">
+      <x:c r="A22" s="8" t="str">
+        <x:v>Orden</x:v>
+      </x:c>
+      <x:c r="B22" s="8" t="str">
+        <x:v>ID</x:v>
+      </x:c>
+      <x:c r="C22" s="8" t="str">
+        <x:v>Historia</x:v>
+      </x:c>
+      <x:c r="D22" s="8" t="str">
+        <x:v>Depende de</x:v>
+      </x:c>
+      <x:c r="E22" s="8" t="str">
+        <x:v>Etapa</x:v>
+      </x:c>
+      <x:c r="F22" s="8" t="str">
+        <x:v>Sprint actual</x:v>
+      </x:c>
+      <x:c r="G22" s="8" t="str">
+        <x:v>Revisión de planificación</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="42" customHeight="1">
+      <x:c r="A23" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B23" s="11" t="str">
+        <x:v>HU-62</x:v>
+      </x:c>
+      <x:c r="C23" s="11" t="str">
+        <x:v>Administrar cuentas del equipo</x:v>
+      </x:c>
+      <x:c r="D23" s="11" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="E23" s="11" t="str">
+        <x:v>Base y permisos</x:v>
+      </x:c>
+      <x:c r="F23" s="11" t="str">
+        <x:v>S1 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G23" s="11" t="str"/>
+    </x:row>
+    <x:row r="24" ht="42" customHeight="1">
+      <x:c r="A24" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B24" s="13" t="str">
+        <x:v>HU-02</x:v>
+      </x:c>
+      <x:c r="C24" s="13" t="str">
+        <x:v>Registrar cliente</x:v>
+      </x:c>
+      <x:c r="D24" s="13" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="E24" s="13" t="str">
+        <x:v>Base y permisos</x:v>
+      </x:c>
+      <x:c r="F24" s="13" t="str">
+        <x:v>S2 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G24" s="13" t="str"/>
+    </x:row>
+    <x:row r="25" ht="42" customHeight="1">
+      <x:c r="A25" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B25" s="11" t="str">
+        <x:v>HU-61</x:v>
+      </x:c>
+      <x:c r="C25" s="11" t="str">
+        <x:v>Registrar local</x:v>
+      </x:c>
+      <x:c r="D25" s="11" t="str">
+        <x:v>HU-02</x:v>
+      </x:c>
+      <x:c r="E25" s="11" t="str">
+        <x:v>Base y permisos</x:v>
+      </x:c>
+      <x:c r="F25" s="11" t="str">
+        <x:v>S2 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G25" s="11" t="str"/>
+    </x:row>
+    <x:row r="26" ht="42" customHeight="1">
+      <x:c r="A26" s="13" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B26" s="13" t="str">
+        <x:v>HU-03</x:v>
+      </x:c>
+      <x:c r="C26" s="13" t="str">
+        <x:v>Registrar equipo</x:v>
+      </x:c>
+      <x:c r="D26" s="13" t="str">
+        <x:v>HU-61</x:v>
+      </x:c>
+      <x:c r="E26" s="13" t="str">
+        <x:v>Base y permisos</x:v>
+      </x:c>
+      <x:c r="F26" s="13" t="str">
+        <x:v>S2 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G26" s="13" t="str"/>
+    </x:row>
+    <x:row r="27" ht="42" customHeight="1">
+      <x:c r="A27" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B27" s="11" t="str">
+        <x:v>HU-63</x:v>
+      </x:c>
+      <x:c r="C27" s="11" t="str">
+        <x:v>Asociar cliente a locales</x:v>
+      </x:c>
+      <x:c r="D27" s="11" t="str">
+        <x:v>HU-02, HU-61, HU-62</x:v>
+      </x:c>
+      <x:c r="E27" s="11" t="str">
+        <x:v>Base y permisos</x:v>
+      </x:c>
+      <x:c r="F27" s="11" t="str">
+        <x:v>S3 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G27" s="11" t="str"/>
+    </x:row>
+    <x:row r="28" ht="42" customHeight="1">
+      <x:c r="A28" s="13" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B28" s="13" t="str">
+        <x:v>HU-01</x:v>
+      </x:c>
+      <x:c r="C28" s="13" t="str">
+        <x:v>Iniciar sesión según perfil</x:v>
+      </x:c>
+      <x:c r="D28" s="13" t="str">
+        <x:v>HU-62</x:v>
+      </x:c>
+      <x:c r="E28" s="13" t="str">
+        <x:v>Base y permisos</x:v>
+      </x:c>
+      <x:c r="F28" s="13" t="str">
+        <x:v>S1 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G28" s="13" t="str"/>
+    </x:row>
+    <x:row r="29" ht="42" customHeight="1">
+      <x:c r="A29" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B29" s="11" t="str">
+        <x:v>HU-64</x:v>
+      </x:c>
+      <x:c r="C29" s="11" t="str">
+        <x:v>Cerrar sesión</x:v>
+      </x:c>
+      <x:c r="D29" s="11" t="str">
+        <x:v>HU-01</x:v>
+      </x:c>
+      <x:c r="E29" s="11" t="str">
+        <x:v>Base y permisos</x:v>
+      </x:c>
+      <x:c r="F29" s="11" t="str">
+        <x:v>S2 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G29" s="11" t="str"/>
+    </x:row>
+    <x:row r="30" ht="42" customHeight="1">
+      <x:c r="A30" s="13" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B30" s="13" t="str">
+        <x:v>HU-59</x:v>
+      </x:c>
+      <x:c r="C30" s="13" t="str">
+        <x:v>Proteger datos locales</x:v>
+      </x:c>
+      <x:c r="D30" s="13" t="str">
+        <x:v>HU-01</x:v>
+      </x:c>
+      <x:c r="E30" s="13" t="str">
+        <x:v>Base y permisos</x:v>
+      </x:c>
+      <x:c r="F30" s="13" t="str">
+        <x:v>S2 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G30" s="13" t="str"/>
+    </x:row>
+    <x:row r="31" ht="42" customHeight="1">
+      <x:c r="A31" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B31" s="11" t="str">
+        <x:v>HU-25</x:v>
+      </x:c>
+      <x:c r="C31" s="11" t="str">
+        <x:v>Actualizar datos de local</x:v>
+      </x:c>
+      <x:c r="D31" s="11" t="str">
+        <x:v>HU-61</x:v>
+      </x:c>
+      <x:c r="E31" s="11" t="str">
+        <x:v>Base y permisos</x:v>
+      </x:c>
+      <x:c r="F31" s="11" t="str">
+        <x:v>S2 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G31" s="11" t="str"/>
+    </x:row>
+    <x:row r="32" ht="42" customHeight="1">
+      <x:c r="A32" s="13" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B32" s="13" t="str">
+        <x:v>HU-26</x:v>
+      </x:c>
+      <x:c r="C32" s="13" t="str">
+        <x:v>Actualizar equipo y mantención</x:v>
+      </x:c>
+      <x:c r="D32" s="13" t="str">
+        <x:v>HU-03</x:v>
+      </x:c>
+      <x:c r="E32" s="13" t="str">
+        <x:v>Base y permisos</x:v>
+      </x:c>
+      <x:c r="F32" s="13" t="str">
+        <x:v>S2 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G32" s="13" t="str"/>
+    </x:row>
+    <x:row r="33" ht="42" customHeight="1">
+      <x:c r="A33" s="11" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B33" s="11" t="str">
+        <x:v>HU-47</x:v>
+      </x:c>
+      <x:c r="C33" s="11" t="str">
+        <x:v>Identificar trabajo exterior</x:v>
+      </x:c>
+      <x:c r="D33" s="11" t="str">
+        <x:v>HU-03</x:v>
+      </x:c>
+      <x:c r="E33" s="11" t="str">
+        <x:v>Base y permisos</x:v>
+      </x:c>
+      <x:c r="F33" s="11" t="str">
+        <x:v>S3 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G33" s="11" t="str"/>
+    </x:row>
+    <x:row r="34" ht="42" customHeight="1">
+      <x:c r="A34" s="13" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B34" s="13" t="str">
+        <x:v>HU-04</x:v>
+      </x:c>
+      <x:c r="C34" s="13" t="str">
+        <x:v>Crear OT</x:v>
+      </x:c>
+      <x:c r="D34" s="13" t="str">
+        <x:v>HU-01, HU-03</x:v>
+      </x:c>
+      <x:c r="E34" s="13" t="str">
+        <x:v>Planificación</x:v>
+      </x:c>
+      <x:c r="F34" s="13" t="str">
+        <x:v>S2 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G34" s="13" t="str"/>
+    </x:row>
+    <x:row r="35" ht="42" customHeight="1">
+      <x:c r="A35" s="11" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B35" s="11" t="str">
+        <x:v>HU-24</x:v>
+      </x:c>
+      <x:c r="C35" s="11" t="str">
+        <x:v>Restringir fotos y ubicación por OT</x:v>
+      </x:c>
+      <x:c r="D35" s="11" t="str">
+        <x:v>HU-01, HU-04</x:v>
+      </x:c>
+      <x:c r="E35" s="11" t="str">
+        <x:v>Base y permisos</x:v>
+      </x:c>
+      <x:c r="F35" s="11" t="str">
+        <x:v>S3 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G35" s="11" t="str"/>
+    </x:row>
+    <x:row r="36" ht="42" customHeight="1">
+      <x:c r="A36" s="13" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B36" s="13" t="str">
+        <x:v>HU-20</x:v>
+      </x:c>
+      <x:c r="C36" s="13" t="str">
+        <x:v>Alertar clima al planificar</x:v>
+      </x:c>
+      <x:c r="D36" s="13" t="str">
+        <x:v>HU-04, HU-47</x:v>
+      </x:c>
+      <x:c r="E36" s="13" t="str">
+        <x:v>Planificación</x:v>
+      </x:c>
+      <x:c r="F36" s="13" t="str">
+        <x:v>S4 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G36" s="13" t="str"/>
+    </x:row>
+    <x:row r="37" ht="42" customHeight="1">
+      <x:c r="A37" s="11" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B37" s="11" t="str">
+        <x:v>HU-48</x:v>
+      </x:c>
+      <x:c r="C37" s="11" t="str">
+        <x:v>Ver vigencia del pronóstico</x:v>
+      </x:c>
+      <x:c r="D37" s="11" t="str">
+        <x:v>HU-20</x:v>
+      </x:c>
+      <x:c r="E37" s="11" t="str">
+        <x:v>Planificación</x:v>
+      </x:c>
+      <x:c r="F37" s="11" t="str">
+        <x:v>S4 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G37" s="11" t="str"/>
+    </x:row>
+    <x:row r="38" ht="42" customHeight="1">
+      <x:c r="A38" s="13" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B38" s="13" t="str">
+        <x:v>HU-29</x:v>
+      </x:c>
+      <x:c r="C38" s="13" t="str">
+        <x:v>Consultar carga por técnico</x:v>
+      </x:c>
+      <x:c r="D38" s="13" t="str">
+        <x:v>HU-04, HU-62</x:v>
+      </x:c>
+      <x:c r="E38" s="13" t="str">
+        <x:v>Planificación</x:v>
+      </x:c>
+      <x:c r="F38" s="13" t="str">
+        <x:v>S3 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G38" s="13" t="str"/>
+    </x:row>
+    <x:row r="39" ht="42" customHeight="1">
+      <x:c r="A39" s="11" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B39" s="11" t="str">
+        <x:v>HU-30</x:v>
+      </x:c>
+      <x:c r="C39" s="11" t="str">
+        <x:v>Validar asignación</x:v>
+      </x:c>
+      <x:c r="D39" s="11" t="str">
+        <x:v>HU-04</x:v>
+      </x:c>
+      <x:c r="E39" s="11" t="str">
+        <x:v>Planificación</x:v>
+      </x:c>
+      <x:c r="F39" s="11" t="str">
+        <x:v>S2 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G39" s="11" t="str"/>
+    </x:row>
+    <x:row r="40" ht="42" customHeight="1">
+      <x:c r="A40" s="13" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B40" s="13" t="str">
+        <x:v>HU-05</x:v>
+      </x:c>
+      <x:c r="C40" s="13" t="str">
+        <x:v>Asignar OT a técnico</x:v>
+      </x:c>
+      <x:c r="D40" s="13" t="str">
+        <x:v>HU-30</x:v>
+      </x:c>
+      <x:c r="E40" s="13" t="str">
+        <x:v>Planificación</x:v>
+      </x:c>
+      <x:c r="F40" s="13" t="str">
+        <x:v>S2 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G40" s="13" t="str"/>
+    </x:row>
+    <x:row r="41" ht="42" customHeight="1">
+      <x:c r="A41" s="11" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B41" s="11" t="str">
+        <x:v>HU-06</x:v>
+      </x:c>
+      <x:c r="C41" s="11" t="str">
+        <x:v>Reprogramar OT</x:v>
+      </x:c>
+      <x:c r="D41" s="11" t="str">
+        <x:v>HU-05</x:v>
+      </x:c>
+      <x:c r="E41" s="11" t="str">
+        <x:v>Planificación</x:v>
+      </x:c>
+      <x:c r="F41" s="11" t="str">
+        <x:v>S4 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G41" s="11" t="str"/>
+    </x:row>
+    <x:row r="42" ht="42" customHeight="1">
+      <x:c r="A42" s="13" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B42" s="13" t="str">
+        <x:v>HU-50</x:v>
+      </x:c>
+      <x:c r="C42" s="13" t="str">
+        <x:v>Revisar alerta al reprogramar</x:v>
+      </x:c>
+      <x:c r="D42" s="13" t="str">
+        <x:v>HU-06, HU-20</x:v>
+      </x:c>
+      <x:c r="E42" s="13" t="str">
+        <x:v>Planificación</x:v>
+      </x:c>
+      <x:c r="F42" s="13" t="str">
+        <x:v>S5 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G42" s="13" t="str"/>
+    </x:row>
+    <x:row r="43" ht="42" customHeight="1">
+      <x:c r="A43" s="11" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B43" s="11" t="str">
+        <x:v>HU-65</x:v>
+      </x:c>
+      <x:c r="C43" s="11" t="str">
+        <x:v>Cancelar OT</x:v>
+      </x:c>
+      <x:c r="D43" s="11" t="str">
+        <x:v>HU-05</x:v>
+      </x:c>
+      <x:c r="E43" s="11" t="str">
+        <x:v>Planificación</x:v>
+      </x:c>
+      <x:c r="F43" s="11" t="str">
+        <x:v>S4 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G43" s="11" t="str"/>
+    </x:row>
+    <x:row r="44" ht="42" customHeight="1">
+      <x:c r="A44" s="13" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B44" s="13" t="str">
+        <x:v>HU-07</x:v>
+      </x:c>
+      <x:c r="C44" s="13" t="str">
+        <x:v>Consultar mis OT</x:v>
+      </x:c>
+      <x:c r="D44" s="13" t="str">
+        <x:v>HU-01, HU-05</x:v>
+      </x:c>
+      <x:c r="E44" s="13" t="str">
+        <x:v>Preparar visita</x:v>
+      </x:c>
+      <x:c r="F44" s="13" t="str">
+        <x:v>S2 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G44" s="13" t="str"/>
+    </x:row>
+    <x:row r="45" ht="42" customHeight="1">
+      <x:c r="A45" s="11" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B45" s="11" t="str">
+        <x:v>HU-08</x:v>
+      </x:c>
+      <x:c r="C45" s="11" t="str">
+        <x:v>Consultar detalle de OT</x:v>
+      </x:c>
+      <x:c r="D45" s="11" t="str">
+        <x:v>HU-07</x:v>
+      </x:c>
+      <x:c r="E45" s="11" t="str">
+        <x:v>Preparar visita</x:v>
+      </x:c>
+      <x:c r="F45" s="11" t="str">
+        <x:v>S1 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G45" s="11" t="str"/>
+    </x:row>
+    <x:row r="46" ht="42" customHeight="1">
+      <x:c r="A46" s="13" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B46" s="13" t="str">
+        <x:v>HU-27</x:v>
+      </x:c>
+      <x:c r="C46" s="13" t="str">
+        <x:v>Consultar equipos de un local</x:v>
+      </x:c>
+      <x:c r="D46" s="13" t="str">
+        <x:v>HU-03, HU-08</x:v>
+      </x:c>
+      <x:c r="E46" s="13" t="str">
+        <x:v>Preparar visita</x:v>
+      </x:c>
+      <x:c r="F46" s="13" t="str">
+        <x:v>S2 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G46" s="13" t="str"/>
+    </x:row>
+    <x:row r="47" ht="42" customHeight="1">
+      <x:c r="A47" s="11" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B47" s="11" t="str">
+        <x:v>HU-39</x:v>
+      </x:c>
+      <x:c r="C47" s="11" t="str">
+        <x:v>Preparar OT sin conexión</x:v>
+      </x:c>
+      <x:c r="D47" s="11" t="str">
+        <x:v>HU-05, HU-03, HU-59</x:v>
+      </x:c>
+      <x:c r="E47" s="11" t="str">
+        <x:v>Preparar visita</x:v>
+      </x:c>
+      <x:c r="F47" s="11" t="str">
+        <x:v>S2 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G47" s="11" t="str"/>
+    </x:row>
+    <x:row r="48" ht="42" customHeight="1">
+      <x:c r="A48" s="13" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B48" s="13" t="str">
+        <x:v>HU-31</x:v>
+      </x:c>
+      <x:c r="C48" s="13" t="str">
+        <x:v>Avisar cambios de agenda</x:v>
+      </x:c>
+      <x:c r="D48" s="13" t="str">
+        <x:v>HU-06, HU-39</x:v>
+      </x:c>
+      <x:c r="E48" s="13" t="str">
+        <x:v>Planificación</x:v>
+      </x:c>
+      <x:c r="F48" s="13" t="str">
+        <x:v>S4 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G48" s="13" t="str"/>
+    </x:row>
+    <x:row r="49" ht="42" customHeight="1">
+      <x:c r="A49" s="11" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B49" s="11" t="str">
+        <x:v>HU-09</x:v>
+      </x:c>
+      <x:c r="C49" s="11" t="str">
+        <x:v>Aceptar OT</x:v>
+      </x:c>
+      <x:c r="D49" s="11" t="str">
+        <x:v>HU-07, HU-05</x:v>
+      </x:c>
+      <x:c r="E49" s="11" t="str">
+        <x:v>Preparar visita</x:v>
+      </x:c>
+      <x:c r="F49" s="11" t="str">
+        <x:v>S2 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G49" s="11" t="str"/>
+    </x:row>
+    <x:row r="50" ht="42" customHeight="1">
+      <x:c r="A50" s="13" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B50" s="13" t="str">
+        <x:v>HU-49</x:v>
+      </x:c>
+      <x:c r="C50" s="13" t="str">
+        <x:v>Alertar al técnico</x:v>
+      </x:c>
+      <x:c r="D50" s="13" t="str">
+        <x:v>HU-20, HU-08</x:v>
+      </x:c>
+      <x:c r="E50" s="13" t="str">
+        <x:v>Preparar visita</x:v>
+      </x:c>
+      <x:c r="F50" s="13" t="str">
+        <x:v>S4 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G50" s="13" t="str"/>
+    </x:row>
+    <x:row r="51" ht="42" customHeight="1">
+      <x:c r="A51" s="11" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B51" s="11" t="str">
+        <x:v>HU-33</x:v>
+      </x:c>
+      <x:c r="C51" s="11" t="str">
+        <x:v>Iniciar intervención</x:v>
+      </x:c>
+      <x:c r="D51" s="11" t="str">
+        <x:v>HU-09</x:v>
+      </x:c>
+      <x:c r="E51" s="11" t="str">
+        <x:v>Intervención</x:v>
+      </x:c>
+      <x:c r="F51" s="11" t="str">
+        <x:v>S2 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G51" s="11" t="str"/>
+    </x:row>
+    <x:row r="52" ht="42" customHeight="1">
+      <x:c r="A52" s="13" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B52" s="13" t="str">
+        <x:v>HU-57</x:v>
+      </x:c>
+      <x:c r="C52" s="13" t="str">
+        <x:v>Solicitar permiso de ubicación</x:v>
+      </x:c>
+      <x:c r="D52" s="13" t="str">
+        <x:v>HU-33</x:v>
+      </x:c>
+      <x:c r="E52" s="13" t="str">
+        <x:v>Intervención</x:v>
+      </x:c>
+      <x:c r="F52" s="13" t="str">
+        <x:v>S2 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G52" s="13" t="str"/>
+    </x:row>
+    <x:row r="53" ht="42" customHeight="1">
+      <x:c r="A53" s="11" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B53" s="11" t="str">
+        <x:v>HU-10</x:v>
+      </x:c>
+      <x:c r="C53" s="11" t="str">
+        <x:v>Registrar check-in</x:v>
+      </x:c>
+      <x:c r="D53" s="11" t="str">
+        <x:v>HU-33, HU-57</x:v>
+      </x:c>
+      <x:c r="E53" s="11" t="str">
+        <x:v>Intervención</x:v>
+      </x:c>
+      <x:c r="F53" s="11" t="str">
+        <x:v>S2 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G53" s="11" t="str"/>
+    </x:row>
+    <x:row r="54" ht="42" customHeight="1">
+      <x:c r="A54" s="13" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B54" s="13" t="str">
+        <x:v>HU-34</x:v>
+      </x:c>
+      <x:c r="C54" s="13" t="str">
+        <x:v>Continuar borrador</x:v>
+      </x:c>
+      <x:c r="D54" s="13" t="str">
+        <x:v>HU-33</x:v>
+      </x:c>
+      <x:c r="E54" s="13" t="str">
+        <x:v>Intervención</x:v>
+      </x:c>
+      <x:c r="F54" s="13" t="str">
+        <x:v>S2 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G54" s="13" t="str"/>
+    </x:row>
+    <x:row r="55" ht="42" customHeight="1">
+      <x:c r="A55" s="11" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B55" s="11" t="str">
+        <x:v>HU-11</x:v>
+      </x:c>
+      <x:c r="C55" s="11" t="str">
+        <x:v>Registrar diagnóstico</x:v>
+      </x:c>
+      <x:c r="D55" s="11" t="str">
+        <x:v>HU-34</x:v>
+      </x:c>
+      <x:c r="E55" s="11" t="str">
+        <x:v>Intervención</x:v>
+      </x:c>
+      <x:c r="F55" s="11" t="str">
+        <x:v>S2 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G55" s="11" t="str"/>
+    </x:row>
+    <x:row r="56" ht="42" customHeight="1">
+      <x:c r="A56" s="13" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B56" s="13" t="str">
+        <x:v>HU-12</x:v>
+      </x:c>
+      <x:c r="C56" s="13" t="str">
+        <x:v>Registrar actividades</x:v>
+      </x:c>
+      <x:c r="D56" s="13" t="str">
+        <x:v>HU-34</x:v>
+      </x:c>
+      <x:c r="E56" s="13" t="str">
+        <x:v>Intervención</x:v>
+      </x:c>
+      <x:c r="F56" s="13" t="str">
+        <x:v>S2 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G56" s="13" t="str"/>
+    </x:row>
+    <x:row r="57" ht="42" customHeight="1">
+      <x:c r="A57" s="11" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B57" s="11" t="str">
+        <x:v>HU-67</x:v>
+      </x:c>
+      <x:c r="C57" s="11" t="str">
+        <x:v>Registrar materiales usados</x:v>
+      </x:c>
+      <x:c r="D57" s="11" t="str">
+        <x:v>HU-34</x:v>
+      </x:c>
+      <x:c r="E57" s="11" t="str">
+        <x:v>Intervención</x:v>
+      </x:c>
+      <x:c r="F57" s="11" t="str">
+        <x:v>S2 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G57" s="11" t="str"/>
+    </x:row>
+    <x:row r="58" ht="42" customHeight="1">
+      <x:c r="A58" s="13" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B58" s="13" t="str">
+        <x:v>HU-38</x:v>
+      </x:c>
+      <x:c r="C58" s="13" t="str">
+        <x:v>Formulario de registro rápido</x:v>
+      </x:c>
+      <x:c r="D58" s="13" t="str">
+        <x:v>HU-33</x:v>
+      </x:c>
+      <x:c r="E58" s="13" t="str">
+        <x:v>Intervención</x:v>
+      </x:c>
+      <x:c r="F58" s="13" t="str">
+        <x:v>S3 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G58" s="13" t="str"/>
+    </x:row>
+    <x:row r="59" ht="42" customHeight="1">
+      <x:c r="A59" s="11" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B59" s="11" t="str">
+        <x:v>HU-13</x:v>
+      </x:c>
+      <x:c r="C59" s="11" t="str">
+        <x:v>Adjuntar fotos</x:v>
+      </x:c>
+      <x:c r="D59" s="11" t="str">
+        <x:v>HU-33, HU-24, HU-59</x:v>
+      </x:c>
+      <x:c r="E59" s="11" t="str">
+        <x:v>Intervención</x:v>
+      </x:c>
+      <x:c r="F59" s="11" t="str">
+        <x:v>S3 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G59" s="11" t="str"/>
+    </x:row>
+    <x:row r="60" ht="42" customHeight="1">
+      <x:c r="A60" s="13" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B60" s="13" t="str">
+        <x:v>HU-36</x:v>
+      </x:c>
+      <x:c r="C60" s="13" t="str">
+        <x:v>Distinguir fotos antes y después</x:v>
+      </x:c>
+      <x:c r="D60" s="13" t="str">
+        <x:v>HU-13</x:v>
+      </x:c>
+      <x:c r="E60" s="13" t="str">
+        <x:v>Intervención</x:v>
+      </x:c>
+      <x:c r="F60" s="13" t="str">
+        <x:v>S4 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G60" s="13" t="str"/>
+    </x:row>
+    <x:row r="61" ht="42" customHeight="1">
+      <x:c r="A61" s="11" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B61" s="11" t="str">
+        <x:v>HU-66</x:v>
+      </x:c>
+      <x:c r="C61" s="11" t="str">
+        <x:v>Registrar check-out</x:v>
+      </x:c>
+      <x:c r="D61" s="11" t="str">
+        <x:v>HU-10</x:v>
+      </x:c>
+      <x:c r="E61" s="11" t="str">
+        <x:v>Intervención</x:v>
+      </x:c>
+      <x:c r="F61" s="11" t="str">
+        <x:v>S2 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G61" s="11" t="str"/>
+    </x:row>
+    <x:row r="62" ht="42" customHeight="1">
+      <x:c r="A62" s="13" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B62" s="13" t="str">
+        <x:v>HU-43</x:v>
+      </x:c>
+      <x:c r="C62" s="13" t="str">
+        <x:v>Conservar hora original</x:v>
+      </x:c>
+      <x:c r="D62" s="13" t="str">
+        <x:v>HU-10, HU-66</x:v>
+      </x:c>
+      <x:c r="E62" s="13" t="str">
+        <x:v>Intervención</x:v>
+      </x:c>
+      <x:c r="F62" s="13" t="str">
+        <x:v>S3 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G62" s="13" t="str"/>
+    </x:row>
+    <x:row r="63" ht="42" customHeight="1">
+      <x:c r="A63" s="11" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B63" s="11" t="str">
+        <x:v>HU-35</x:v>
+      </x:c>
+      <x:c r="C63" s="11" t="str">
+        <x:v>Registrar visitas adicionales</x:v>
+      </x:c>
+      <x:c r="D63" s="11" t="str">
+        <x:v>HU-33, HU-66</x:v>
+      </x:c>
+      <x:c r="E63" s="11" t="str">
+        <x:v>Intervención</x:v>
+      </x:c>
+      <x:c r="F63" s="11" t="str">
+        <x:v>S4 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G63" s="11" t="str"/>
+    </x:row>
+    <x:row r="64" ht="42" customHeight="1">
+      <x:c r="A64" s="13" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B64" s="13" t="str">
+        <x:v>HU-37</x:v>
+      </x:c>
+      <x:c r="C64" s="13" t="str">
+        <x:v>Revisar resumen antes de enviar</x:v>
+      </x:c>
+      <x:c r="D64" s="13" t="str">
+        <x:v>HU-10, HU-11, HU-12, HU-13, HU-66, HU-67</x:v>
+      </x:c>
+      <x:c r="E64" s="13" t="str">
+        <x:v>Intervención</x:v>
+      </x:c>
+      <x:c r="F64" s="13" t="str">
+        <x:v>S3 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G64" s="13" t="str"/>
+    </x:row>
+    <x:row r="65" ht="42" customHeight="1">
+      <x:c r="A65" s="11" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B65" s="11" t="str">
+        <x:v>HU-15</x:v>
+      </x:c>
+      <x:c r="C65" s="11" t="str">
+        <x:v>Guardar visita sin conexión</x:v>
+      </x:c>
+      <x:c r="D65" s="11" t="str">
+        <x:v>HU-39, HU-10, HU-11, HU-12, HU-13, HU-66, HU-67, HU-43</x:v>
+      </x:c>
+      <x:c r="E65" s="11" t="str">
+        <x:v>Intervención</x:v>
+      </x:c>
+      <x:c r="F65" s="11" t="str">
+        <x:v>S3 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G65" s="11" t="str"/>
+    </x:row>
+    <x:row r="66" ht="42" customHeight="1">
+      <x:c r="A66" s="13" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B66" s="13" t="str">
+        <x:v>HU-14</x:v>
+      </x:c>
+      <x:c r="C66" s="13" t="str">
+        <x:v>Enviar cierre técnico</x:v>
+      </x:c>
+      <x:c r="D66" s="13" t="str">
+        <x:v>HU-37, HU-15</x:v>
+      </x:c>
+      <x:c r="E66" s="13" t="str">
+        <x:v>Intervención</x:v>
+      </x:c>
+      <x:c r="F66" s="13" t="str">
+        <x:v>S3 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G66" s="13" t="str"/>
+    </x:row>
+    <x:row r="67" ht="42" customHeight="1">
+      <x:c r="A67" s="11" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B67" s="11" t="str">
+        <x:v>HU-16</x:v>
+      </x:c>
+      <x:c r="C67" s="11" t="str">
+        <x:v>Sincronizar automáticamente</x:v>
+      </x:c>
+      <x:c r="D67" s="11" t="str">
+        <x:v>HU-15</x:v>
+      </x:c>
+      <x:c r="E67" s="11" t="str">
+        <x:v>Sincronización</x:v>
+      </x:c>
+      <x:c r="F67" s="11" t="str">
+        <x:v>S3 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G67" s="11" t="str"/>
+    </x:row>
+    <x:row r="68" ht="42" customHeight="1">
+      <x:c r="A68" s="13" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B68" s="13" t="str">
+        <x:v>HU-40</x:v>
+      </x:c>
+      <x:c r="C68" s="13" t="str">
+        <x:v>Reintentar envío fallido</x:v>
+      </x:c>
+      <x:c r="D68" s="13" t="str">
+        <x:v>HU-16</x:v>
+      </x:c>
+      <x:c r="E68" s="13" t="str">
+        <x:v>Sincronización</x:v>
+      </x:c>
+      <x:c r="F68" s="13" t="str">
+        <x:v>S3 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G68" s="13" t="str"/>
+    </x:row>
+    <x:row r="69" ht="42" customHeight="1">
+      <x:c r="A69" s="11" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B69" s="11" t="str">
+        <x:v>HU-42</x:v>
+      </x:c>
+      <x:c r="C69" s="11" t="str">
+        <x:v>Sincronizar fotos pendientes</x:v>
+      </x:c>
+      <x:c r="D69" s="11" t="str">
+        <x:v>HU-16, HU-13</x:v>
+      </x:c>
+      <x:c r="E69" s="11" t="str">
+        <x:v>Sincronización</x:v>
+      </x:c>
+      <x:c r="F69" s="11" t="str">
+        <x:v>S3 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G69" s="11" t="str"/>
+    </x:row>
+    <x:row r="70" ht="42" customHeight="1">
+      <x:c r="A70" s="13" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B70" s="13" t="str">
+        <x:v>HU-17</x:v>
+      </x:c>
+      <x:c r="C70" s="13" t="str">
+        <x:v>Ver estado de sincronización</x:v>
+      </x:c>
+      <x:c r="D70" s="13" t="str">
+        <x:v>HU-16, HU-42</x:v>
+      </x:c>
+      <x:c r="E70" s="13" t="str">
+        <x:v>Sincronización</x:v>
+      </x:c>
+      <x:c r="F70" s="13" t="str">
+        <x:v>S3 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G70" s="13" t="str"/>
+    </x:row>
+    <x:row r="71" ht="42" customHeight="1">
+      <x:c r="A71" s="11" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B71" s="11" t="str">
+        <x:v>HU-32</x:v>
+      </x:c>
+      <x:c r="C71" s="11" t="str">
+        <x:v>Ver estado operativo de OT</x:v>
+      </x:c>
+      <x:c r="D71" s="11" t="str">
+        <x:v>HU-05, HU-16</x:v>
+      </x:c>
+      <x:c r="E71" s="11" t="str">
+        <x:v>Sincronización</x:v>
+      </x:c>
+      <x:c r="F71" s="11" t="str">
+        <x:v>S3 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G71" s="11" t="str"/>
+    </x:row>
+    <x:row r="72" ht="42" customHeight="1">
+      <x:c r="A72" s="13" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B72" s="13" t="str">
+        <x:v>HU-58</x:v>
+      </x:c>
+      <x:c r="C72" s="13" t="str">
+        <x:v>Restringir acceso a fotos</x:v>
+      </x:c>
+      <x:c r="D72" s="13" t="str">
+        <x:v>HU-13, HU-24</x:v>
+      </x:c>
+      <x:c r="E72" s="13" t="str">
+        <x:v>Sincronización</x:v>
+      </x:c>
+      <x:c r="F72" s="13" t="str">
+        <x:v>S4 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G72" s="13" t="str"/>
+    </x:row>
+    <x:row r="73" ht="42" customHeight="1">
+      <x:c r="A73" s="11" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B73" s="11" t="str">
+        <x:v>HU-41</x:v>
+      </x:c>
+      <x:c r="C73" s="11" t="str">
+        <x:v>Resolver conflicto de OT</x:v>
+      </x:c>
+      <x:c r="D73" s="11" t="str">
+        <x:v>HU-16</x:v>
+      </x:c>
+      <x:c r="E73" s="11" t="str">
+        <x:v>Sincronización</x:v>
+      </x:c>
+      <x:c r="F73" s="11" t="str">
+        <x:v>S5 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G73" s="11" t="str"/>
+    </x:row>
+    <x:row r="74" ht="42" customHeight="1">
+      <x:c r="A74" s="13" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B74" s="13" t="str">
+        <x:v>HU-18</x:v>
+      </x:c>
+      <x:c r="C74" s="13" t="str">
+        <x:v>Consultar OT propias</x:v>
+      </x:c>
+      <x:c r="D74" s="13" t="str">
+        <x:v>HU-01, HU-63, HU-32</x:v>
+      </x:c>
+      <x:c r="E74" s="13" t="str">
+        <x:v>Conformidad</x:v>
+      </x:c>
+      <x:c r="F74" s="13" t="str">
+        <x:v>S4 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G74" s="13" t="str"/>
+    </x:row>
+    <x:row r="75" ht="42" customHeight="1">
+      <x:c r="A75" s="11" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B75" s="11" t="str">
+        <x:v>HU-44</x:v>
+      </x:c>
+      <x:c r="C75" s="11" t="str">
+        <x:v>Revisar intervención recibida</x:v>
+      </x:c>
+      <x:c r="D75" s="11" t="str">
+        <x:v>HU-18, HU-14, HU-42, HU-58</x:v>
+      </x:c>
+      <x:c r="E75" s="11" t="str">
+        <x:v>Conformidad</x:v>
+      </x:c>
+      <x:c r="F75" s="11" t="str">
+        <x:v>S4 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G75" s="11" t="str"/>
+    </x:row>
+    <x:row r="76" ht="42" customHeight="1">
+      <x:c r="A76" s="13" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B76" s="13" t="str">
+        <x:v>HU-19</x:v>
+      </x:c>
+      <x:c r="C76" s="13" t="str">
+        <x:v>Aprobar conformidad</x:v>
+      </x:c>
+      <x:c r="D76" s="13" t="str">
+        <x:v>HU-44</x:v>
+      </x:c>
+      <x:c r="E76" s="13" t="str">
+        <x:v>Conformidad</x:v>
+      </x:c>
+      <x:c r="F76" s="13" t="str">
+        <x:v>S4 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G76" s="13" t="str"/>
+    </x:row>
+    <x:row r="77" ht="42" customHeight="1">
+      <x:c r="A77" s="11" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B77" s="11" t="str">
+        <x:v>HU-68</x:v>
+      </x:c>
+      <x:c r="C77" s="11" t="str">
+        <x:v>Registrar observaciones</x:v>
+      </x:c>
+      <x:c r="D77" s="11" t="str">
+        <x:v>HU-44</x:v>
+      </x:c>
+      <x:c r="E77" s="11" t="str">
+        <x:v>Conformidad</x:v>
+      </x:c>
+      <x:c r="F77" s="11" t="str">
+        <x:v>S4 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G77" s="11" t="str"/>
+    </x:row>
+    <x:row r="78" ht="42" customHeight="1">
+      <x:c r="A78" s="13" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B78" s="13" t="str">
+        <x:v>HU-45</x:v>
+      </x:c>
+      <x:c r="C78" s="13" t="str">
+        <x:v>Responder observaciones</x:v>
+      </x:c>
+      <x:c r="D78" s="13" t="str">
+        <x:v>HU-68</x:v>
+      </x:c>
+      <x:c r="E78" s="13" t="str">
+        <x:v>Conformidad</x:v>
+      </x:c>
+      <x:c r="F78" s="13" t="str">
+        <x:v>S5 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G78" s="13" t="str"/>
+    </x:row>
+    <x:row r="79" ht="42" customHeight="1">
+      <x:c r="A79" s="11" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B79" s="11" t="str">
+        <x:v>HU-46</x:v>
+      </x:c>
+      <x:c r="C79" s="11" t="str">
+        <x:v>Cerrar OT conforme</x:v>
+      </x:c>
+      <x:c r="D79" s="11" t="str">
+        <x:v>HU-19, HU-45</x:v>
+      </x:c>
+      <x:c r="E79" s="11" t="str">
+        <x:v>Conformidad</x:v>
+      </x:c>
+      <x:c r="F79" s="11" t="str">
+        <x:v>S5 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G79" s="11" t="str"/>
+    </x:row>
+    <x:row r="80" ht="42" customHeight="1">
+      <x:c r="A80" s="13" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B80" s="13" t="str">
+        <x:v>HU-23</x:v>
+      </x:c>
+      <x:c r="C80" s="13" t="str">
+        <x:v>Ver historial de OT</x:v>
+      </x:c>
+      <x:c r="D80" s="13" t="str">
+        <x:v>HU-14</x:v>
+      </x:c>
+      <x:c r="E80" s="13" t="str">
+        <x:v>Seguimiento</x:v>
+      </x:c>
+      <x:c r="F80" s="13" t="str">
+        <x:v>S3 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G80" s="13" t="str"/>
+    </x:row>
+    <x:row r="81" ht="42" customHeight="1">
+      <x:c r="A81" s="11" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B81" s="11" t="str">
+        <x:v>HU-55</x:v>
+      </x:c>
+      <x:c r="C81" s="11" t="str">
+        <x:v>Historial de eventos offline</x:v>
+      </x:c>
+      <x:c r="D81" s="11" t="str">
+        <x:v>HU-23, HU-43, HU-16</x:v>
+      </x:c>
+      <x:c r="E81" s="11" t="str">
+        <x:v>Seguimiento</x:v>
+      </x:c>
+      <x:c r="F81" s="11" t="str">
+        <x:v>S5 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G81" s="11" t="str"/>
+    </x:row>
+    <x:row r="82" ht="42" customHeight="1">
+      <x:c r="A82" s="13" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B82" s="13" t="str">
+        <x:v>HU-56</x:v>
+      </x:c>
+      <x:c r="C82" s="13" t="str">
+        <x:v>Auditar correcciones</x:v>
+      </x:c>
+      <x:c r="D82" s="13" t="str">
+        <x:v>HU-23</x:v>
+      </x:c>
+      <x:c r="E82" s="13" t="str">
+        <x:v>Seguimiento</x:v>
+      </x:c>
+      <x:c r="F82" s="13" t="str">
+        <x:v>S6 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G82" s="13" t="str"/>
+    </x:row>
+    <x:row r="83" ht="42" customHeight="1">
+      <x:c r="A83" s="11" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B83" s="11" t="str">
+        <x:v>HU-21</x:v>
+      </x:c>
+      <x:c r="C83" s="11" t="str">
+        <x:v>Consultar duración de atención</x:v>
+      </x:c>
+      <x:c r="D83" s="11" t="str">
+        <x:v>HU-10, HU-66, HU-43</x:v>
+      </x:c>
+      <x:c r="E83" s="11" t="str">
+        <x:v>Seguimiento</x:v>
+      </x:c>
+      <x:c r="F83" s="11" t="str">
+        <x:v>S4 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G83" s="11" t="str"/>
+    </x:row>
+    <x:row r="84" ht="42" customHeight="1">
+      <x:c r="A84" s="13" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B84" s="13" t="str">
+        <x:v>HU-51</x:v>
+      </x:c>
+      <x:c r="C84" s="13" t="str">
+        <x:v>Configurar política SLA</x:v>
+      </x:c>
+      <x:c r="D84" s="13" t="str">
+        <x:v>HU-02</x:v>
+      </x:c>
+      <x:c r="E84" s="13" t="str">
+        <x:v>Seguimiento</x:v>
+      </x:c>
+      <x:c r="F84" s="13" t="str">
+        <x:v>S5 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G84" s="13" t="str"/>
+    </x:row>
+    <x:row r="85" ht="42" customHeight="1">
+      <x:c r="A85" s="11" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B85" s="11" t="str">
+        <x:v>HU-52</x:v>
+      </x:c>
+      <x:c r="C85" s="11" t="str">
+        <x:v>Medir tiempo de respuesta</x:v>
+      </x:c>
+      <x:c r="D85" s="11" t="str">
+        <x:v>HU-51, HU-10, HU-43</x:v>
+      </x:c>
+      <x:c r="E85" s="11" t="str">
+        <x:v>Seguimiento</x:v>
+      </x:c>
+      <x:c r="F85" s="11" t="str">
+        <x:v>S5 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G85" s="11" t="str"/>
+    </x:row>
+    <x:row r="86" ht="42" customHeight="1">
+      <x:c r="A86" s="13" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B86" s="13" t="str">
+        <x:v>HU-53</x:v>
+      </x:c>
+      <x:c r="C86" s="13" t="str">
+        <x:v>Medir tiempo de resolución</x:v>
+      </x:c>
+      <x:c r="D86" s="13" t="str">
+        <x:v>HU-51, HU-46, HU-43</x:v>
+      </x:c>
+      <x:c r="E86" s="13" t="str">
+        <x:v>Seguimiento</x:v>
+      </x:c>
+      <x:c r="F86" s="13" t="str">
+        <x:v>S5 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G86" s="13" t="str"/>
+    </x:row>
+    <x:row r="87" ht="42" customHeight="1">
+      <x:c r="A87" s="11" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B87" s="11" t="str">
+        <x:v>HU-22</x:v>
+      </x:c>
+      <x:c r="C87" s="11" t="str">
+        <x:v>Consultar cumplimiento SLA</x:v>
+      </x:c>
+      <x:c r="D87" s="11" t="str">
+        <x:v>HU-52, HU-53</x:v>
+      </x:c>
+      <x:c r="E87" s="11" t="str">
+        <x:v>Seguimiento</x:v>
+      </x:c>
+      <x:c r="F87" s="11" t="str">
+        <x:v>S5 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G87" s="11" t="str"/>
+    </x:row>
+    <x:row r="88" ht="42" customHeight="1">
+      <x:c r="A88" s="13" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B88" s="13" t="str">
+        <x:v>HU-54</x:v>
+      </x:c>
+      <x:c r="C88" s="13" t="str">
+        <x:v>Exportar reporte por cliente</x:v>
+      </x:c>
+      <x:c r="D88" s="13" t="str">
+        <x:v>HU-21, HU-22</x:v>
+      </x:c>
+      <x:c r="E88" s="13" t="str">
+        <x:v>Seguimiento</x:v>
+      </x:c>
+      <x:c r="F88" s="13" t="str">
+        <x:v>S6 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G88" s="13" t="str"/>
+    </x:row>
+    <x:row r="89" ht="42" customHeight="1">
+      <x:c r="A89" s="11" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B89" s="11" t="str">
+        <x:v>HU-28</x:v>
+      </x:c>
+      <x:c r="C89" s="11" t="str">
+        <x:v>Buscar y filtrar OT</x:v>
+      </x:c>
+      <x:c r="D89" s="11" t="str">
+        <x:v>HU-32</x:v>
+      </x:c>
+      <x:c r="E89" s="11" t="str">
+        <x:v>Seguimiento</x:v>
+      </x:c>
+      <x:c r="F89" s="11" t="str">
+        <x:v>S3 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G89" s="11" t="str"/>
+    </x:row>
+    <x:row r="90" ht="42" customHeight="1">
+      <x:c r="A90" s="13" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B90" s="13" t="str">
+        <x:v>HU-60</x:v>
+      </x:c>
+      <x:c r="C90" s="13" t="str">
+        <x:v>Gestionar retención de evidencias</x:v>
+      </x:c>
+      <x:c r="D90" s="13" t="str">
+        <x:v>HU-58, HU-23</x:v>
+      </x:c>
+      <x:c r="E90" s="13" t="str">
+        <x:v>Seguimiento</x:v>
+      </x:c>
+      <x:c r="F90" s="13" t="str">
+        <x:v>S6 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G90" s="13" t="str"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B91" t="str">
+        <x:v>HU-69</x:v>
+      </x:c>
+      <x:c r="C91" t="str">
+        <x:v>Consultar agenda diaria</x:v>
+      </x:c>
+      <x:c r="D91" t="str">
+        <x:v>HU-05, HU-07</x:v>
+      </x:c>
+      <x:c r="E91" t="str">
+        <x:v>Planificación y agenda</x:v>
+      </x:c>
+      <x:c r="F91" t="str">
+        <x:v>S3 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G91" t="str">
+        <x:v>Nueva historia: orden visual de las visitas.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B92" t="str">
+        <x:v>HU-70</x:v>
+      </x:c>
+      <x:c r="C92" t="str">
+        <x:v>Registrar visita no ejecutada</x:v>
+      </x:c>
+      <x:c r="D92" t="str">
+        <x:v>HU-05, HU-15, HU-32</x:v>
+      </x:c>
+      <x:c r="E92" t="str">
+        <x:v>Ejecución en terreno</x:v>
+      </x:c>
+      <x:c r="F92" t="str">
+        <x:v>S4 (propuesto)</x:v>
+      </x:c>
+      <x:c r="G92" t="str">
+        <x:v>Nueva historia: requiere motivo y conserva el registro.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>